--- a/data/results/larva_batch_summary.xlsx
+++ b/data/results/larva_batch_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,40 +474,45 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>cohort</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>genotype</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>replicate</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>noise_scale_mm</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>n_flagged_events</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>flagged</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>flag_reason</t>
         </is>
@@ -516,154 +521,148 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N2_nSybxRalRNAi_L1_FA.csv</t>
+          <t>..\data\csvs\N1_nSybxRalRNAiBL29580_29C_L1_FA.csv</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>5402</v>
       </c>
       <c r="C2" t="n">
-        <v>2.665679378008145</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>139.1071954077461</v>
+        <v>113.9853976782455</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7948982594728351</v>
+        <v>0.6331349621083807</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5909314681078609</v>
+        <v>0.5028916384273823</v>
       </c>
       <c r="K2" t="n">
-        <v>4.621558178796428</v>
+        <v>3.760664834839667</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>N1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>0.002482600000011854</v>
+          <t>nSybxRalRNAiBL29580</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>29C_L1_FA</t>
+        </is>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
-      </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
+        <v>0.008951141596470501</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N2_RalG0501_L3_FA.csv</t>
+          <t>..\data\csvs\N1_nSybxRalRNAiBL29580_29C_L2_FA.csv</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5402</v>
+        <v>5403</v>
       </c>
       <c r="C3" t="n">
-        <v>8.978156238430211</v>
+        <v>76.73514714047751</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>81.8</v>
       </c>
       <c r="E3" t="n">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="F3" t="n">
-        <v>541</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>117.2355825991218</v>
+        <v>53.79191090480974</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7193838163169675</v>
+        <v>1.289973882609346</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4743416490252637</v>
+        <v>0.9904544411531474</v>
       </c>
       <c r="K3" t="n">
-        <v>9.916577030407417</v>
+        <v>5.589105474044938</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>N1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>RalG0501</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>0.02086079999999377</v>
+          <t>nSybxRalRNAiBL29580</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>29C_L2_FA</t>
+        </is>
       </c>
       <c r="Q3" t="n">
-        <v>45</v>
-      </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
+        <v>0.004965200000006068</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N3_nSybxRalRNAi_L1_FA.csv</t>
+          <t>..\data\csvs\N1_nSybxRalRNAiBL29580_29C_L3_FA.csv</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5402</v>
+        <v>5403</v>
       </c>
       <c r="C4" t="n">
-        <v>100</v>
+        <v>21.09938922820655</v>
       </c>
       <c r="D4" t="n">
-        <v>180.0666666666667</v>
+        <v>38</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -672,63 +671,62 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+        <v>87.16689580927807</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.6139955093398315</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.4743416490252165</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.891336531321556</v>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>0.3</v>
+          <t>nSybxRalRNAiBL29580</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>29C_L3_FA</t>
+        </is>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="b">
-        <v>1</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0.008951141596460717</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N3_nSybxRalRNAi_L5_FA.csv</t>
+          <t>..\data\csvs\N1_nSybxRalRNAiBL29580_29C_L4_FA.csv</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>5402</v>
       </c>
       <c r="C5" t="n">
-        <v>66.45686782673084</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>115.2666666666667</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -737,69 +735,62 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>60.66819777971884</v>
+        <v>69.24885158806589</v>
       </c>
       <c r="I5" t="n">
-        <v>1.00666257377852</v>
+        <v>0.3846446116722786</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7523961722390666</v>
+        <v>0.276586333718905</v>
       </c>
       <c r="K5" t="n">
-        <v>4.884199013144294</v>
+        <v>7.942241497209713</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N1</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>L5</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>0.004965200000006068</v>
+          <t>nSybxRalRNAiBL29580</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>29C_L4_FA</t>
+        </is>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="b">
-        <v>1</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0.01279888697242738</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N3_W1118_L1_FA.csv</t>
+          <t>..\data\csvs\N1_nSybxRalRNAiBL29580_29C_L5_FA.csv</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>5403</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>19.23005737553211</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>34.63333333333333</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -808,65 +799,62 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>128.4803376256184</v>
+        <v>93.82556110788447</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7135153885169477</v>
+        <v>0.6457368279964519</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5316013544001889</v>
+        <v>0.5239274758971829</v>
       </c>
       <c r="K6" t="n">
-        <v>3.730147450168578</v>
+        <v>3.833079701754197</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>W1118</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>0.009930399999994496</v>
+          <t>nSybxRalRNAiBL29580</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>29C_L5_FA</t>
+        </is>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="inlineStr"/>
+        <v>0.007447800000000282</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>nSybxRalRNAiBL29580_29C_L4_FA.csv</t>
+          <t>..\data\csvs\N1_nSybxRalRNAiBL29580_29C_L6_FA.csv</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5402</v>
+        <v>5403</v>
       </c>
       <c r="C7" t="n">
-        <v>10.19992595335061</v>
+        <v>19.78530446048492</v>
       </c>
       <c r="D7" t="n">
-        <v>5.266666666666667</v>
+        <v>35.63333333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -875,106 +863,728 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>81.70658659105626</v>
+        <v>85.3292753092116</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5067598920263982</v>
+        <v>0.5907865818777632</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3612478373638298</v>
+        <v>0.4509988913511996</v>
       </c>
       <c r="K7" t="n">
-        <v>4.103425398371565</v>
+        <v>3.872208672062936</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>nSybxRalRNAiBL29580</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>29C_L4_FA</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>0.0168955999999959</v>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>29C_L6_FA</t>
+        </is>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" t="inlineStr"/>
+        <v>0.007447800000000282</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>w1118_L1_FA.csv</t>
+          <t>..\data\csvs\N2_nSybxRalRNAi_L1_FA.csv</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5403</v>
+        <v>5402</v>
       </c>
       <c r="C8" t="n">
-        <v>90.098093651675</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>88.26666666666667</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F8" t="n">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>14.80431565580715</v>
+        <v>143.5257002386665</v>
       </c>
       <c r="I8" t="n">
-        <v>0.882961172314542</v>
+        <v>0.7972173684799103</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4883646178829399</v>
+        <v>0.6007495318348902</v>
       </c>
       <c r="K8" t="n">
-        <v>7.379104366384932</v>
+        <v>4.718400152594072</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>w1118</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>FA</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
-        <v>0.03193485089120134</v>
-      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>14</v>
-      </c>
-      <c r="R8" t="b">
+        <v>0.002482600000011854</v>
+      </c>
+      <c r="R8" t="n">
         <v>1</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>..\data\csvs\N2_nSybxRalRNAi_L2_FA.csv</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C9" t="n">
+        <v>50.0925583117364</v>
+      </c>
+      <c r="D9" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>127.869193080765</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.424461861278481</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.224132345786134</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.846383497513595</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>0.007447800000000282</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>unusually fast median speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>..\data\csvs\N2_nSybxRalRNAi_L3_FA.csv</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5404</v>
+      </c>
+      <c r="C10" t="n">
+        <v>62.76831976313841</v>
+      </c>
+      <c r="D10" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>64.07607585567288</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9558837770612564</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7648529270386402</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.413267497929511</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="n">
+        <v>0.004965199999988428</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>..\data\csvs\N2_nSybxRalRNAi_L4_FA.csv</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C11" t="n">
+        <v>31.28470936690115</v>
+      </c>
+      <c r="D11" t="n">
+        <v>46.46666666666667</v>
+      </c>
+      <c r="E11" t="n">
+        <v>64</v>
+      </c>
+      <c r="F11" t="n">
+        <v>36</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>121.7477918360766</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.984748922912456</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.7874642849043526</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.368239935025239</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>..\data\csvs\N2_nSybxRalRNAi_L5_FA.csv</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>106.2824328467211</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.590348636437999</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4589117562233681</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.384928733742462</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="n">
+        <v>0.004965199999997248</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>..\data\csvs\N2_nSybxRalRNAi_L6_FA.csv</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C13" t="n">
+        <v>13.90225842280637</v>
+      </c>
+      <c r="D13" t="n">
+        <v>25.03333333333333</v>
+      </c>
+      <c r="E13" t="n">
+        <v>13</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>120.1010818984415</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.7750123589918789</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.6000000000000085</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.098234988699556</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="n">
+        <v>0.002482599999998624</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>..\data\csvs\N2_nSybxRalRNAi_L7_FA.csv</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C14" t="n">
+        <v>54.09107737874861</v>
+      </c>
+      <c r="D14" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="E14" t="n">
+        <v>113</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>67.95863427939746</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8224118710697556</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.6007495318351138</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.158004329002184</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="n">
+        <v>0.002482600000011854</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>..\data\csvs\N2_nSybxRalRNAi_L8_FA.csv</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5401</v>
+      </c>
+      <c r="C15" t="n">
+        <v>25.01388631734864</v>
+      </c>
+      <c r="D15" t="n">
+        <v>45.03333333333333</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>111.3886815264712</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.825509003407642</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.61846584384272</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.272762572388041</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="n">
+        <v>0.004965199999988428</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>..\data\csvs\N2_nSybxRalRNAi_L9_FA.csv</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>94.57955518017006</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.5258314780217016</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.4013710789368652</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.294267748681114</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="n">
+        <v>0.007447800000000282</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>..\data\csvs\N3_nSybxRalRNAi_L1_FA.csv</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>87.21447328052088</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.4844351413470888</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.3710795063056035</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.142133033466354</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="n">
+        <v>0.007447800000000282</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/results/larva_batch_summary.xlsx
+++ b/data/results/larva_batch_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1586,6 +1586,74 @@
       </c>
       <c r="T17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>..\data\csvs\N3_nSybxRalRNAi_L2_FA.csv</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C18" t="n">
+        <v>27.78600518326546</v>
+      </c>
+      <c r="D18" t="n">
+        <v>50.03333333333333</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>72.04662166194157</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.5542047820149353</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.4242640687118441</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.012573650552031</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="n">
+        <v>0.007021853179890999</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/results/larva_batch_summary.xlsx
+++ b/data/results/larva_batch_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T18"/>
+  <dimension ref="A1:T37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,7 +521,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>..\data\csvs\N1_nSybxRalRNAiBL29580_29C_L1_FA.csv</t>
+          <t>..\data\csvs\genotiponovo\N1\N1_nSybxRalRNAiBL29580_29C_L1_FA.csv</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -561,7 +561,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>nSybxRalRNAiBL29580</t>
+          <t>genotiponovo</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>..\data\csvs\N1_nSybxRalRNAiBL29580_29C_L2_FA.csv</t>
+          <t>..\data\csvs\genotiponovo\N1\N1_nSybxRalRNAiBL29580_29C_L2_FA.csv</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>nSybxRalRNAiBL29580</t>
+          <t>genotiponovo</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -649,7 +649,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>..\data\csvs\N1_nSybxRalRNAiBL29580_29C_L3_FA.csv</t>
+          <t>..\data\csvs\genotiponovo\N1\N1_nSybxRalRNAiBL29580_29C_L3_FA.csv</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -689,7 +689,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>nSybxRalRNAiBL29580</t>
+          <t>genotiponovo</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -713,7 +713,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>..\data\csvs\N1_nSybxRalRNAiBL29580_29C_L4_FA.csv</t>
+          <t>..\data\csvs\genotiponovo\N1\N1_nSybxRalRNAiBL29580_29C_L4_FA.csv</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -753,7 +753,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>nSybxRalRNAiBL29580</t>
+          <t>genotiponovo</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -777,7 +777,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>..\data\csvs\N1_nSybxRalRNAiBL29580_29C_L5_FA.csv</t>
+          <t>..\data\csvs\genotiponovo\N1\N1_nSybxRalRNAiBL29580_29C_L5_FA.csv</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -817,7 +817,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>nSybxRalRNAiBL29580</t>
+          <t>genotiponovo</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -841,7 +841,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>..\data\csvs\N1_nSybxRalRNAiBL29580_29C_L6_FA.csv</t>
+          <t>..\data\csvs\genotiponovo\N1\N1_nSybxRalRNAiBL29580_29C_L6_FA.csv</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>nSybxRalRNAiBL29580</t>
+          <t>genotiponovo</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -905,7 +905,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>..\data\csvs\N2_nSybxRalRNAi_L1_FA.csv</t>
+          <t>..\data\csvs\genotiponovo\N2\N2_nSybxRalRNAi_L1_FA.csv</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -945,7 +945,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>genotiponovo</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -973,7 +973,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>..\data\csvs\N2_nSybxRalRNAi_L2_FA.csv</t>
+          <t>..\data\csvs\genotiponovo\N2\N2_nSybxRalRNAi_L2_FA.csv</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>genotiponovo</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1045,7 +1045,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>..\data\csvs\N2_nSybxRalRNAi_L3_FA.csv</t>
+          <t>..\data\csvs\genotiponovo\N2\N2_nSybxRalRNAi_L3_FA.csv</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>genotiponovo</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1113,7 +1113,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>..\data\csvs\N2_nSybxRalRNAi_L4_FA.csv</t>
+          <t>..\data\csvs\genotiponovo\N2\N2_nSybxRalRNAi_L4_FA.csv</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>genotiponovo</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1181,7 +1181,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>..\data\csvs\N2_nSybxRalRNAi_L5_FA.csv</t>
+          <t>..\data\csvs\genotiponovo\N2\N2_nSybxRalRNAi_L5_FA.csv</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>genotiponovo</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1249,7 +1249,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>..\data\csvs\N2_nSybxRalRNAi_L6_FA.csv</t>
+          <t>..\data\csvs\genotiponovo\N2\N2_nSybxRalRNAi_L6_FA.csv</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>genotiponovo</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>..\data\csvs\N2_nSybxRalRNAi_L7_FA.csv</t>
+          <t>..\data\csvs\genotiponovo\N2\N2_nSybxRalRNAi_L7_FA.csv</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>genotiponovo</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1385,7 +1385,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>..\data\csvs\N2_nSybxRalRNAi_L8_FA.csv</t>
+          <t>..\data\csvs\genotiponovo\N2\N2_nSybxRalRNAi_L8_FA.csv</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>genotiponovo</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1453,7 +1453,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>..\data\csvs\N2_nSybxRalRNAi_L9_FA.csv</t>
+          <t>..\data\csvs\genotiponovo\N2\N2_nSybxRalRNAi_L9_FA.csv</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>genotiponovo</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1521,7 +1521,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>..\data\csvs\N3_nSybxRalRNAi_L1_FA.csv</t>
+          <t>..\data\csvs\genotiponovo\N3\N3_nSybxRalRNAi_L1_FA.csv</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>genotiponovo</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1589,7 +1589,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>..\data\csvs\N3_nSybxRalRNAi_L2_FA.csv</t>
+          <t>..\data\csvs\genotiponovo\N3\N3_nSybxRalRNAi_L2_FA.csv</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>genotiponovo</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1653,6 +1653,1278 @@
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>..\data\csvs\genotiponovo\N3\N3_nSybxRalRNAi_L3_FA.csv</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C19" t="n">
+        <v>38.68937430581266</v>
+      </c>
+      <c r="D19" t="n">
+        <v>52.16666666666666</v>
+      </c>
+      <c r="E19" t="n">
+        <v>43</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>68.68420079634333</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.6227035430312178</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.4459820624195625</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.947708195903186</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>genotiponovo</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="n">
+        <v>0.004965200000023708</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>..\data\csvs\nSybxRalRNAi\N1\N1_nSybxRalRNAiBL29580_29C_L1_FA.csv</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>113.9853976782455</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.6331349621083807</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.5028916384273823</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.760664834839667</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>29C_L1_FA</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.008951141596470501</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>..\data\csvs\nSybxRalRNAi\N1\N1_nSybxRalRNAiBL29580_29C_L2_FA.csv</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5403</v>
+      </c>
+      <c r="C21" t="n">
+        <v>76.73514714047751</v>
+      </c>
+      <c r="D21" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="E21" t="n">
+        <v>72</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>53.79191090480974</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.289973882609346</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.9904544411531474</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5.589105474044938</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>29C_L2_FA</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.004965200000006068</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>..\data\csvs\nSybxRalRNAi\N1\N1_nSybxRalRNAiBL29580_29C_L3_FA.csv</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5403</v>
+      </c>
+      <c r="C22" t="n">
+        <v>21.09938922820655</v>
+      </c>
+      <c r="D22" t="n">
+        <v>38</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>87.16689580927807</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.6139955093398315</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.4743416490252165</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.891336531321556</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>29C_L3_FA</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.008951141596460717</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>..\data\csvs\nSybxRalRNAi\N1\N1_nSybxRalRNAiBL29580_29C_L4_FA.csv</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>69.24885158806589</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.3846446116722786</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.276586333718905</v>
+      </c>
+      <c r="K23" t="n">
+        <v>7.942241497209713</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>29C_L4_FA</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.01279888697242738</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>..\data\csvs\nSybxRalRNAi\N1\N1_nSybxRalRNAiBL29580_29C_L5_FA.csv</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>5403</v>
+      </c>
+      <c r="C24" t="n">
+        <v>19.23005737553211</v>
+      </c>
+      <c r="D24" t="n">
+        <v>34.63333333333333</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>93.82556110788447</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.6457368279964519</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.5239274758971829</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.833079701754197</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>29C_L5_FA</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.007447800000000282</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>..\data\csvs\nSybxRalRNAi\N1\N1_nSybxRalRNAiBL29580_29C_L6_FA.csv</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>5403</v>
+      </c>
+      <c r="C25" t="n">
+        <v>19.78530446048492</v>
+      </c>
+      <c r="D25" t="n">
+        <v>35.63333333333333</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>85.3292753092116</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.5907865818777632</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.4509988913511996</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.872208672062936</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>29C_L6_FA</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.007447800000000282</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>..\data\csvs\nSybxRalRNAi\N2\N2_nSybxRalRNAi_L1_FA.csv</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>17</v>
+      </c>
+      <c r="F26" t="n">
+        <v>17</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>143.5257002386665</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.7972173684799103</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.6007495318348902</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.718400152594072</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="n">
+        <v>0.002482600000011854</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>..\data\csvs\nSybxRalRNAi\N2\N2_nSybxRalRNAi_L2_FA.csv</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C27" t="n">
+        <v>50.0925583117364</v>
+      </c>
+      <c r="D27" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>127.869193080765</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.424461861278481</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.224132345786134</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5.846383497513595</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="n">
+        <v>0.007447800000000282</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>unusually fast median speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>..\data\csvs\nSybxRalRNAi\N2\N2_nSybxRalRNAi_L3_FA.csv</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>5404</v>
+      </c>
+      <c r="C28" t="n">
+        <v>62.76831976313841</v>
+      </c>
+      <c r="D28" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>13</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>64.07607585567288</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.9558837770612564</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.7648529270386402</v>
+      </c>
+      <c r="K28" t="n">
+        <v>6.413267497929511</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="n">
+        <v>0.004965199999988428</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>..\data\csvs\nSybxRalRNAi\N2\N2_nSybxRalRNAi_L4_FA.csv</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C29" t="n">
+        <v>31.28470936690115</v>
+      </c>
+      <c r="D29" t="n">
+        <v>46.46666666666667</v>
+      </c>
+      <c r="E29" t="n">
+        <v>64</v>
+      </c>
+      <c r="F29" t="n">
+        <v>36</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>121.7477918360766</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.984748922912456</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.7874642849043526</v>
+      </c>
+      <c r="K29" t="n">
+        <v>5.368239935025239</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>..\data\csvs\nSybxRalRNAi\N2\N2_nSybxRalRNAi_L5_FA.csv</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>106.2824328467211</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.590348636437999</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.4589117562233681</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4.384928733742462</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="n">
+        <v>0.004965199999997248</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>..\data\csvs\nSybxRalRNAi\N2\N2_nSybxRalRNAi_L6_FA.csv</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C31" t="n">
+        <v>13.90225842280637</v>
+      </c>
+      <c r="D31" t="n">
+        <v>25.03333333333333</v>
+      </c>
+      <c r="E31" t="n">
+        <v>13</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>120.1010818984415</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.7750123589918789</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.6000000000000085</v>
+      </c>
+      <c r="K31" t="n">
+        <v>5.098234988699556</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="n">
+        <v>0.002482599999998624</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>..\data\csvs\nSybxRalRNAi\N2\N2_nSybxRalRNAi_L7_FA.csv</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C32" t="n">
+        <v>54.09107737874861</v>
+      </c>
+      <c r="D32" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="E32" t="n">
+        <v>113</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>67.95863427939746</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.8224118710697556</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.6007495318351138</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.158004329002184</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="n">
+        <v>0.002482600000011854</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>..\data\csvs\nSybxRalRNAi\N2\N2_nSybxRalRNAi_L8_FA.csv</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>5401</v>
+      </c>
+      <c r="C33" t="n">
+        <v>25.01388631734864</v>
+      </c>
+      <c r="D33" t="n">
+        <v>45.03333333333333</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>111.3886815264712</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.825509003407642</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.61846584384272</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4.272762572388041</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="n">
+        <v>0.004965199999988428</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>..\data\csvs\nSybxRalRNAi\N2\N2_nSybxRalRNAi_L9_FA.csv</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="E34" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>94.57955518017006</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.5258314780217016</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.4013710789368652</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.294267748681114</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="n">
+        <v>0.007447800000000282</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>..\data\csvs\nSybxRalRNAi\N3\N3_nSybxRalRNAi_L1_FA.csv</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>87.21447328052088</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.4844351413470888</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.3710795063056035</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.142133033466354</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="n">
+        <v>0.007447800000000282</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>..\data\csvs\nSybxRalRNAi\N3\N3_nSybxRalRNAi_L2_FA.csv</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C36" t="n">
+        <v>27.78600518326546</v>
+      </c>
+      <c r="D36" t="n">
+        <v>50.03333333333333</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>72.04662166194157</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.5542047820149353</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.4242640687118441</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.012573650552031</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="n">
+        <v>0.007021853179890999</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>..\data\csvs\nSybxRalRNAi\N3\N3_nSybxRalRNAi_L3_FA.csv</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C37" t="n">
+        <v>38.68937430581266</v>
+      </c>
+      <c r="D37" t="n">
+        <v>52.16666666666666</v>
+      </c>
+      <c r="E37" t="n">
+        <v>43</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>68.68420079634333</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.6227035430312178</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.4459820624195625</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.947708195903186</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="n">
+        <v>0.004965200000023708</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/results/larva_batch_summary.xlsx
+++ b/data/results/larva_batch_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T37"/>
+  <dimension ref="A1:T92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,20 +521,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>..\data\csvs\genotiponovo\N1\N1_nSybxRalRNAiBL29580_29C_L1_FA.csv</t>
+          <t>..\data\csvs\graph 1\RalG0501\N1\L1.csv</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>5402</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.3517215845982969</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>7.033333333333333</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>794</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -543,16 +543,16 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>113.9853976782455</v>
+        <v>98.28030882272476</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6331349621083807</v>
+        <v>0.5478278083763921</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5028916384273823</v>
+        <v>0.3900000000000421</v>
       </c>
       <c r="K2" t="n">
-        <v>3.760664834839667</v>
+        <v>3.812833591962552</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -561,18 +561,18 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>genotiponovo</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>RalG0501</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>29C_L1_FA</t>
-        </is>
-      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>0.008951141596470501</v>
+        <v>0.01241299999998871</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -585,38 +585,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>..\data\csvs\genotiponovo\N1\N1_nSybxRalRNAiBL29580_29C_L2_FA.csv</t>
+          <t>..\data\csvs\graph 1\RalG0501\N1\L2.csv</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>5403</v>
       </c>
       <c r="C3" t="n">
-        <v>76.73514714047751</v>
+        <v>0.2220988339811216</v>
       </c>
       <c r="D3" t="n">
-        <v>81.8</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E3" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>53.79191090480974</v>
+        <v>104.7843791721658</v>
       </c>
       <c r="I3" t="n">
-        <v>1.289973882609346</v>
+        <v>0.5832154684907185</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9904544411531474</v>
+        <v>0.4509988913511996</v>
       </c>
       <c r="K3" t="n">
-        <v>5.589105474044938</v>
+        <v>4.443748417721254</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,21 +625,21 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>genotiponovo</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>RalG0501</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>29C_L2_FA</t>
-        </is>
-      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>0.004965200000006068</v>
+        <v>0.01824614369812799</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S3" t="b">
         <v>0</v>
@@ -649,38 +649,38 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>..\data\csvs\genotiponovo\N1\N1_nSybxRalRNAiBL29580_29C_L3_FA.csv</t>
+          <t>..\data\csvs\graph 1\RalG0501\N1\L3.csv</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5403</v>
+        <v>5402</v>
       </c>
       <c r="C4" t="n">
-        <v>21.09938922820655</v>
+        <v>19.71492039985191</v>
       </c>
       <c r="D4" t="n">
-        <v>38</v>
+        <v>22.03333333333333</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>409</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>87.16689580927807</v>
+        <v>78.63007562022435</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6139955093398315</v>
+        <v>0.5440272759701869</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4743416490252165</v>
+        <v>0.4297665493272367</v>
       </c>
       <c r="K4" t="n">
-        <v>3.891336531321556</v>
+        <v>3.07467071407653</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -689,44 +689,48 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>genotiponovo</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>RalG0501</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>29C_L3_FA</t>
-        </is>
-      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>0.008951141596460717</v>
+        <v>0.01336921015018389</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S4" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>..\data\csvs\genotiponovo\N1\N1_nSybxRalRNAiBL29580_29C_L4_FA.csv</t>
+          <t>..\data\csvs\graph 1\RalG0501\N1\L4.csv</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>5402</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>12.45834875971862</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>20.93333333333333</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1432</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -735,16 +739,16 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>69.24885158806589</v>
+        <v>61.42067522566082</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3846446116722786</v>
+        <v>0.3897250966095229</v>
       </c>
       <c r="J5" t="n">
-        <v>0.276586333718905</v>
+        <v>0.2418677324488687</v>
       </c>
       <c r="K5" t="n">
-        <v>7.942241497209713</v>
+        <v>4.263801121065659</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -753,62 +757,66 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>genotiponovo</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>RalG0501</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>29C_L4_FA</t>
-        </is>
-      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>0.01279888697242738</v>
+        <v>0.01241300000000635</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>..\data\csvs\genotiponovo\N1\N1_nSybxRalRNAiBL29580_29C_L5_FA.csv</t>
+          <t>..\data\csvs\graph 1\RalG0501\N1\L5.csv</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5403</v>
+        <v>5402</v>
       </c>
       <c r="C6" t="n">
-        <v>19.23005737553211</v>
+        <v>0.1851166234727878</v>
       </c>
       <c r="D6" t="n">
-        <v>34.63333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>93.82556110788447</v>
+        <v>100.7494620368079</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6457368279964519</v>
+        <v>0.5606536562983189</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5239274758971829</v>
+        <v>0.4295346318982424</v>
       </c>
       <c r="K6" t="n">
-        <v>3.833079701754197</v>
+        <v>3.712371209887228</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -817,21 +825,21 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>genotiponovo</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>RalG0501</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>29C_L5_FA</t>
-        </is>
-      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>0.007447800000000282</v>
+        <v>0.01689560000000301</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S6" t="b">
         <v>0</v>
@@ -841,17 +849,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>..\data\csvs\genotiponovo\N1\N1_nSybxRalRNAiBL29580_29C_L6_FA.csv</t>
+          <t>..\data\csvs\graph 1\RalG0501\N1\L6.csv</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5403</v>
+        <v>5402</v>
       </c>
       <c r="C7" t="n">
-        <v>19.78530446048492</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>35.63333333333333</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -863,16 +871,16 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>85.3292753092116</v>
+        <v>123.4994085479989</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5907865818777632</v>
+        <v>0.6859807917867002</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4509988913511996</v>
+        <v>0.5161395160225938</v>
       </c>
       <c r="K7" t="n">
-        <v>3.872208672062936</v>
+        <v>4.902407571795773</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -881,18 +889,18 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>genotiponovo</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>RalG0501</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>29C_L6_FA</t>
-        </is>
-      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="n">
-        <v>0.007447800000000282</v>
+        <v>0.0174243183126165</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -905,7 +913,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>..\data\csvs\genotiponovo\N2\N2_nSybxRalRNAi_L1_FA.csv</t>
+          <t>..\data\csvs\graph 1\RalG0501\N2\L1.csv</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -918,25 +926,25 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>143.5257002386665</v>
+        <v>123.764500379386</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7972173684799103</v>
+        <v>0.6874532515055692</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6007495318348902</v>
+        <v>0.5316013544001889</v>
       </c>
       <c r="K8" t="n">
-        <v>4.718400152594072</v>
+        <v>4.956631920972262</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -945,7 +953,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>genotiponovo</t>
+          <t>RalG0501</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -953,17 +961,13 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>0.002482600000011854</v>
+        <v>0.01510106625771797</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="b">
         <v>0</v>
@@ -973,20 +977,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>..\data\csvs\genotiponovo\N2\N2_nSybxRalRNAi_L2_FA.csv</t>
+          <t>..\data\csvs\graph 1\RalG0501\N2\L2.csv</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5402</v>
+        <v>5403</v>
       </c>
       <c r="C9" t="n">
-        <v>50.0925583117364</v>
+        <v>50.06477882657783</v>
       </c>
       <c r="D9" t="n">
-        <v>47.5</v>
+        <v>90.16666666666667</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -995,16 +999,16 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>127.869193080765</v>
+        <v>64.79859693700487</v>
       </c>
       <c r="I9" t="n">
-        <v>1.424461861278481</v>
+        <v>0.7207852829477739</v>
       </c>
       <c r="J9" t="n">
-        <v>1.224132345786134</v>
+        <v>0.5307541803885919</v>
       </c>
       <c r="K9" t="n">
-        <v>5.846383497513595</v>
+        <v>4.443647150708517</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1013,7 +1017,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>genotiponovo</t>
+          <t>RalG0501</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1021,11 +1025,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="n">
         <v>0.007447800000000282</v>
@@ -1038,27 +1038,27 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>unusually fast median speed</t>
+          <t>high untracked %</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>..\data\csvs\genotiponovo\N2\N2_nSybxRalRNAi_L3_FA.csv</t>
+          <t>..\data\csvs\graph 1\RalG0501\N2\L3.csv</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5404</v>
+        <v>5402</v>
       </c>
       <c r="C10" t="n">
-        <v>62.76831976313841</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>112.5</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1067,16 +1067,16 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>64.07607585567288</v>
+        <v>89.59403194659993</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9558837770612564</v>
+        <v>0.49765246406184</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7648529270386402</v>
+        <v>0.3899999999999601</v>
       </c>
       <c r="K10" t="n">
-        <v>6.413267497929511</v>
+        <v>3.747238983571816</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>genotiponovo</t>
+          <t>RalG0501</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1093,14 +1093,10 @@
           <t>L3</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
-        <v>0.004965199999988428</v>
+        <v>0.01361846625772432</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1113,38 +1109,38 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>..\data\csvs\genotiponovo\N2\N2_nSybxRalRNAi_L4_FA.csv</t>
+          <t>..\data\csvs\graph 1\RalG0501\N2\L4.csv</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>5402</v>
       </c>
       <c r="C11" t="n">
-        <v>31.28470936690115</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>46.46666666666667</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>121.7477918360766</v>
+        <v>130.6870617837222</v>
       </c>
       <c r="I11" t="n">
-        <v>0.984748922912456</v>
+        <v>0.7259048053159906</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7874642849043526</v>
+        <v>0.540832691319615</v>
       </c>
       <c r="K11" t="n">
-        <v>5.368239935025239</v>
+        <v>5.022917478916028</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1153,7 +1149,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>genotiponovo</t>
+          <t>RalG0501</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1161,17 +1157,13 @@
           <t>L4</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>0.01404370635979448</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="b">
         <v>0</v>
@@ -1181,11 +1173,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>..\data\csvs\genotiponovo\N2\N2_nSybxRalRNAi_L5_FA.csv</t>
+          <t>..\data\csvs\graph 1\RalG0501\N2\L6.csv</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5402</v>
+        <v>5403</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -1194,25 +1186,25 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>106.2824328467211</v>
+        <v>121.9151474211305</v>
       </c>
       <c r="I12" t="n">
-        <v>0.590348636437999</v>
+        <v>0.6771809706783773</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4589117562233681</v>
+        <v>0.5108815909776654</v>
       </c>
       <c r="K12" t="n">
-        <v>4.384928733742462</v>
+        <v>5.312965273743102</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1221,25 +1213,21 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>genotiponovo</t>
+          <t>RalG0501</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>L5</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="n">
-        <v>0.004965199999997248</v>
+        <v>0.01053277976984274</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="b">
         <v>0</v>
@@ -1249,20 +1237,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>..\data\csvs\genotiponovo\N2\N2_nSybxRalRNAi_L6_FA.csv</t>
+          <t>..\data\csvs\graph 1\RalG0501\N2\L7.csv</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>5402</v>
       </c>
       <c r="C13" t="n">
-        <v>13.90225842280637</v>
+        <v>51.96223620881155</v>
       </c>
       <c r="D13" t="n">
-        <v>25.03333333333333</v>
+        <v>93.13333333333334</v>
       </c>
       <c r="E13" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1271,16 +1259,16 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>120.1010818984415</v>
+        <v>64.79782078763523</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7750123589918789</v>
+        <v>0.7493965395640159</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6000000000000085</v>
+        <v>0.5515432893254391</v>
       </c>
       <c r="K13" t="n">
-        <v>5.098234988699556</v>
+        <v>5.021125371866523</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1289,48 +1277,48 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>genotiponovo</t>
+          <t>RalG0501</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>L6</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="n">
-        <v>0.002482599999998624</v>
+        <v>0.009930399999976856</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="b">
-        <v>0</v>
-      </c>
-      <c r="T13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>..\data\csvs\genotiponovo\N2\N2_nSybxRalRNAi_L7_FA.csv</t>
+          <t>..\data\csvs\graph 1\RalG0501\N2\L8.csv</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>5402</v>
       </c>
       <c r="C14" t="n">
-        <v>54.09107737874861</v>
+        <v>9.422436134764903</v>
       </c>
       <c r="D14" t="n">
-        <v>97.40000000000001</v>
+        <v>16.96666666666667</v>
       </c>
       <c r="E14" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1339,16 +1327,16 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>67.95863427939746</v>
+        <v>146.5473183456619</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8224118710697556</v>
+        <v>0.8986957380150976</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6007495318351138</v>
+        <v>0.6579513659837346</v>
       </c>
       <c r="K14" t="n">
-        <v>4.158004329002184</v>
+        <v>5.508983572311538</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1357,48 +1345,48 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>genotiponovo</t>
+          <t>RalG0501</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>L7</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+          <t>L8</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="n">
-        <v>0.002482600000011854</v>
+        <v>0.009930399999976856</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
       <c r="S14" t="b">
-        <v>0</v>
-      </c>
-      <c r="T14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>..\data\csvs\genotiponovo\N2\N2_nSybxRalRNAi_L8_FA.csv</t>
+          <t>..\data\csvs\graph 1\RalG0501\N2\L9.csv</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5401</v>
+        <v>5402</v>
       </c>
       <c r="C15" t="n">
-        <v>25.01388631734864</v>
+        <v>52.85079600148093</v>
       </c>
       <c r="D15" t="n">
-        <v>45.03333333333333</v>
+        <v>95.16666666666667</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1407,16 +1395,16 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>111.3886815264712</v>
+        <v>70.59684698774427</v>
       </c>
       <c r="I15" t="n">
-        <v>0.825509003407642</v>
+        <v>0.8318560132098696</v>
       </c>
       <c r="J15" t="n">
-        <v>0.61846584384272</v>
+        <v>0.6184658438425261</v>
       </c>
       <c r="K15" t="n">
-        <v>4.272762572388041</v>
+        <v>4.669218350002479</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1425,35 +1413,35 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>genotiponovo</t>
+          <t>RalG0501</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>L8</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="n">
-        <v>0.004965199999988428</v>
+        <v>0.007447800000000282</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="b">
-        <v>0</v>
-      </c>
-      <c r="T15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>..\data\csvs\genotiponovo\N2\N2_nSybxRalRNAi_L9_FA.csv</t>
+          <t>..\data\csvs\graph 1\RalG0501\N3\L1.csv</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1463,10 +1451,10 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1475,40 +1463,36 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>94.57955518017006</v>
+        <v>80.13809826004909</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5258314780217016</v>
+        <v>0.4451292256621872</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4013710789368652</v>
+        <v>0.3600000000000136</v>
       </c>
       <c r="K16" t="n">
-        <v>3.294267748681114</v>
+        <v>3.026879581351042</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>genotiponovo</t>
+          <t>RalG0501</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>L9</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="n">
-        <v>0.007447800000000282</v>
+        <v>0.01110252472187975</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -1521,7 +1505,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>..\data\csvs\genotiponovo\N3\N3_nSybxRalRNAi_L1_FA.csv</t>
+          <t>..\data\csvs\graph 1\RalG0501\N3\L2.csv</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1543,16 +1527,16 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>87.21447328052088</v>
+        <v>123.9421683358477</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4844351413470888</v>
+        <v>0.688440112956014</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3710795063056035</v>
+        <v>0.5366563145999381</v>
       </c>
       <c r="K17" t="n">
-        <v>3.142133033466354</v>
+        <v>4.118859065323702</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1561,22 +1545,18 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>genotiponovo</t>
+          <t>RalG0501</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="n">
-        <v>0.007447800000000282</v>
+        <v>0.009930399999985677</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -1589,17 +1569,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>..\data\csvs\genotiponovo\N3\N3_nSybxRalRNAi_L2_FA.csv</t>
+          <t>..\data\csvs\graph 1\RalG0501\N3\L4.csv</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>5402</v>
       </c>
       <c r="C18" t="n">
-        <v>27.78600518326546</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>50.03333333333333</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -1611,16 +1591,16 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>72.04662166194157</v>
+        <v>88.81815490888393</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5542047820149353</v>
+        <v>0.4933428341541415</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4242640687118441</v>
+        <v>0.3661966684720482</v>
       </c>
       <c r="K18" t="n">
-        <v>3.012573650552031</v>
+        <v>3.260214716855346</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1629,22 +1609,18 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>genotiponovo</t>
+          <t>RalG0501</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="n">
-        <v>0.007021853179890999</v>
+        <v>0.009930399999994496</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -1657,20 +1633,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>..\data\csvs\genotiponovo\N3\N3_nSybxRalRNAi_L3_FA.csv</t>
+          <t>..\data\csvs\graph 1\RalG0501\N3\L5.csv</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>5402</v>
       </c>
       <c r="C19" t="n">
-        <v>38.68937430581266</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>52.16666666666666</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1679,16 +1655,16 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>68.68420079634333</v>
+        <v>113.4658016968247</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6227035430312178</v>
+        <v>0.6302488522319464</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4459820624195625</v>
+        <v>0.4589117562233681</v>
       </c>
       <c r="K19" t="n">
-        <v>3.947708195903186</v>
+        <v>4.041435388571684</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1697,22 +1673,18 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>genotiponovo</t>
+          <t>RalG0501</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="n">
-        <v>0.004965200000023708</v>
+        <v>0.007447800000000282</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -1725,7 +1697,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>..\data\csvs\nSybxRalRNAi\N1\N1_nSybxRalRNAiBL29580_29C_L1_FA.csv</t>
+          <t>..\data\csvs\graph 1\RalG0501\N3\L6.csv</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1747,36 +1719,36 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>113.9853976782455</v>
+        <v>109.7828852516609</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6331349621083807</v>
+        <v>0.6097919936215196</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5028916384273823</v>
+        <v>0.4569463863517212</v>
       </c>
       <c r="K20" t="n">
-        <v>3.760664834839667</v>
+        <v>5.08382729840426</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>N1</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>RalG0501</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>29C_L1_FA</t>
-        </is>
-      </c>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="n">
-        <v>0.008951141596470501</v>
+        <v>0.007447800000000282</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -1789,20 +1761,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>..\data\csvs\nSybxRalRNAi\N1\N1_nSybxRalRNAiBL29580_29C_L2_FA.csv</t>
+          <t>..\data\csvs\graph 1\RalG0501\N3\L7.csv</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5403</v>
+        <v>5402</v>
       </c>
       <c r="C21" t="n">
-        <v>76.73514714047751</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>81.8</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E21" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1811,36 +1783,36 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>53.79191090480974</v>
+        <v>132.3046362178633</v>
       </c>
       <c r="I21" t="n">
-        <v>1.289973882609346</v>
+        <v>0.734889666087002</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9904544411531474</v>
+        <v>0.5531726674376251</v>
       </c>
       <c r="K21" t="n">
-        <v>5.589105474044938</v>
+        <v>4.966789707648112</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>N1</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>RalG0501</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>29C_L2_FA</t>
-        </is>
-      </c>
+      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="n">
-        <v>0.004965200000006068</v>
+        <v>0.007447800000000282</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -1853,20 +1825,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>..\data\csvs\nSybxRalRNAi\N1\N1_nSybxRalRNAiBL29580_29C_L3_FA.csv</t>
+          <t>..\data\csvs\graph 1\RalG0501\N3\L8.csv</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5403</v>
+        <v>5402</v>
       </c>
       <c r="C22" t="n">
-        <v>21.09938922820655</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1875,36 +1847,36 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>87.16689580927807</v>
+        <v>114.926143996528</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6139955093398315</v>
+        <v>0.6383603628764749</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4743416490252165</v>
+        <v>0.4883646178830577</v>
       </c>
       <c r="K22" t="n">
-        <v>3.891336531321556</v>
+        <v>4.318020379757135</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>N1</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>RalG0501</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>29C_L3_FA</t>
-        </is>
-      </c>
+      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="n">
-        <v>0.008951141596460717</v>
+        <v>0.009930400000012135</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -1917,7 +1889,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>..\data\csvs\nSybxRalRNAi\N1\N1_nSybxRalRNAiBL29580_29C_L4_FA.csv</t>
+          <t>..\data\csvs\graph 1\RalG0501\N3\L9.csv</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1939,36 +1911,36 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>69.24885158806589</v>
+        <v>133.2462151855279</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3846446116722786</v>
+        <v>0.74011969182852</v>
       </c>
       <c r="J23" t="n">
-        <v>0.276586333718905</v>
+        <v>0.5580322571323375</v>
       </c>
       <c r="K23" t="n">
-        <v>7.942241497209713</v>
+        <v>4.295136784783468</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>N1</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>RalG0501</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>29C_L4_FA</t>
-        </is>
-      </c>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="n">
-        <v>0.01279888697242738</v>
+        <v>0.007447800000000282</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -1981,20 +1953,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>..\data\csvs\nSybxRalRNAi\N1\N1_nSybxRalRNAiBL29580_29C_L5_FA.csv</t>
+          <t>..\data\csvs\graph 1\w1118\N1\L2.csv</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5403</v>
+        <v>5402</v>
       </c>
       <c r="C24" t="n">
-        <v>19.23005737553211</v>
+        <v>60.71825249907442</v>
       </c>
       <c r="D24" t="n">
-        <v>34.63333333333333</v>
+        <v>109.3333333333333</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2003,16 +1975,16 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>93.82556110788447</v>
+        <v>72.60225832679761</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6457368279964519</v>
+        <v>1.026906058370546</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5239274758971829</v>
+        <v>0.745184540902613</v>
       </c>
       <c r="K24" t="n">
-        <v>3.833079701754197</v>
+        <v>6.294926528562629</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -2021,16 +1993,16 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>w1118</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>29C_L5_FA</t>
-        </is>
-      </c>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="n">
         <v>0.007447800000000282</v>
       </c>
@@ -2038,45 +2010,49 @@
         <v>0</v>
       </c>
       <c r="S24" t="b">
-        <v>0</v>
-      </c>
-      <c r="T24" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>..\data\csvs\nSybxRalRNAi\N1\N1_nSybxRalRNAiBL29580_29C_L6_FA.csv</t>
+          <t>..\data\csvs\graph 1\w1118\N1\L4.csv</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5403</v>
+        <v>5402</v>
       </c>
       <c r="C25" t="n">
-        <v>19.78530446048492</v>
+        <v>0.6479081821547575</v>
       </c>
       <c r="D25" t="n">
-        <v>35.63333333333333</v>
+        <v>43.7</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1357</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>85.3292753092116</v>
+        <v>120.3520936519898</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5907865818777632</v>
+        <v>0.6728592638016575</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4509988913511996</v>
+        <v>0.4242640687120024</v>
       </c>
       <c r="K25" t="n">
-        <v>3.872208672062936</v>
+        <v>5.035891182303321</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -2085,21 +2061,21 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>w1118</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>29C_L6_FA</t>
-        </is>
-      </c>
+      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="n">
-        <v>0.007447800000000282</v>
+        <v>0.004965200000014888</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S25" t="b">
         <v>0</v>
@@ -2109,65 +2085,61 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>..\data\csvs\nSybxRalRNAi\N2\N2_nSybxRalRNAi_L1_FA.csv</t>
+          <t>..\data\csvs\graph 1\w1118\N1\L5.csv</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5402</v>
+        <v>5403</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.1295576531556543</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>93.66666666666667</v>
       </c>
       <c r="E26" t="n">
-        <v>17</v>
+        <v>3166</v>
       </c>
       <c r="F26" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>143.5257002386665</v>
+        <v>86.98132157917314</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7972173684799103</v>
+        <v>0.4836774137859489</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6007495318348902</v>
+        <v>0.05685600988223756</v>
       </c>
       <c r="K26" t="n">
-        <v>4.718400152594072</v>
+        <v>6.033655608335696</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>N1</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>w1118</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="n">
-        <v>0.002482600000011854</v>
+        <v>0.002482599999994214</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="b">
         <v>0</v>
@@ -2177,20 +2149,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>..\data\csvs\nSybxRalRNAi\N2\N2_nSybxRalRNAi_L2_FA.csv</t>
+          <t>..\data\csvs\graph 1\w1118\N1\L6.csv</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>5402</v>
       </c>
       <c r="C27" t="n">
-        <v>50.0925583117364</v>
+        <v>1.018141429100333</v>
       </c>
       <c r="D27" t="n">
-        <v>47.5</v>
+        <v>7.966666666666667</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1738</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2199,70 +2171,62 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>127.869193080765</v>
+        <v>111.9394488620525</v>
       </c>
       <c r="I27" t="n">
-        <v>1.424461861278481</v>
+        <v>0.6281675020317199</v>
       </c>
       <c r="J27" t="n">
-        <v>1.224132345786134</v>
+        <v>0.4576431721886614</v>
       </c>
       <c r="K27" t="n">
-        <v>5.846383497513595</v>
+        <v>3.570504166080656</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>N1</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>w1118</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="n">
-        <v>0.007447800000000282</v>
+        <v>0.004965199999988428</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
       <c r="S27" t="b">
-        <v>1</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>unusually fast median speed</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>..\data\csvs\nSybxRalRNAi\N2\N2_nSybxRalRNAi_L3_FA.csv</t>
+          <t>..\data\csvs\graph 1\w1118\N1\L7.csv</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5404</v>
+        <v>5402</v>
       </c>
       <c r="C28" t="n">
-        <v>62.76831976313841</v>
+        <v>59.21880784894483</v>
       </c>
       <c r="D28" t="n">
-        <v>112.5</v>
+        <v>105.9333333333333</v>
       </c>
       <c r="E28" t="n">
-        <v>13</v>
+        <v>365</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -2271,84 +2235,84 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>64.07607585567288</v>
+        <v>66.79612448464449</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9558837770612564</v>
+        <v>0.9100289439324863</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7648529270386402</v>
+        <v>0.6113183007860086</v>
       </c>
       <c r="K28" t="n">
-        <v>6.413267497929511</v>
+        <v>5.344043412997553</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>N1</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>w1118</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="n">
-        <v>0.004965199999988428</v>
+        <v>0.005551262360951707</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="b">
-        <v>0</v>
-      </c>
-      <c r="T28" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>..\data\csvs\nSybxRalRNAi\N2\N2_nSybxRalRNAi_L4_FA.csv</t>
+          <t>..\data\csvs\graph 1\w1118\N2\L1.csv</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>5402</v>
       </c>
       <c r="C29" t="n">
-        <v>31.28470936690115</v>
+        <v>15.66086634579785</v>
       </c>
       <c r="D29" t="n">
-        <v>46.46666666666667</v>
+        <v>28.2</v>
       </c>
       <c r="E29" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>121.7477918360766</v>
+        <v>88.13771131337786</v>
       </c>
       <c r="I29" t="n">
-        <v>0.984748922912456</v>
+        <v>0.5804898659497993</v>
       </c>
       <c r="J29" t="n">
-        <v>0.7874642849043526</v>
+        <v>0.436806593356955</v>
       </c>
       <c r="K29" t="n">
-        <v>5.368239935025239</v>
+        <v>4.053998026640029</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2357,45 +2321,45 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>w1118</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>L4</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>0.01053277976984274</v>
       </c>
       <c r="R29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S29" t="b">
-        <v>0</v>
-      </c>
-      <c r="T29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>..\data\csvs\nSybxRalRNAi\N2\N2_nSybxRalRNAi_L5_FA.csv</t>
+          <t>..\data\csvs\graph 1\w1118\N2\L2.csv</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>5402</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>65.69788967049242</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>118.3</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -2407,16 +2371,16 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>106.2824328467211</v>
+        <v>60.56791913616659</v>
       </c>
       <c r="I30" t="n">
-        <v>0.590348636437999</v>
+        <v>0.9811218002618779</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4589117562233681</v>
+        <v>0.7130918594403068</v>
       </c>
       <c r="K30" t="n">
-        <v>4.384928733742462</v>
+        <v>5.616733926402641</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2425,48 +2389,48 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>w1118</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>L5</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="n">
-        <v>0.004965199999997248</v>
+        <v>0.004965200000006068</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
       <c r="S30" t="b">
-        <v>0</v>
-      </c>
-      <c r="T30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>..\data\csvs\nSybxRalRNAi\N2\N2_nSybxRalRNAi_L6_FA.csv</t>
+          <t>..\data\csvs\graph 1\w1118\N2\L3.csv</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5402</v>
+        <v>5401</v>
       </c>
       <c r="C31" t="n">
-        <v>13.90225842280637</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>25.03333333333333</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -2475,16 +2439,16 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>120.1010818984415</v>
+        <v>137.2630290393675</v>
       </c>
       <c r="I31" t="n">
-        <v>0.7750123589918789</v>
+        <v>0.7625723835520416</v>
       </c>
       <c r="J31" t="n">
-        <v>0.6000000000000085</v>
+        <v>0.5531726674375326</v>
       </c>
       <c r="K31" t="n">
-        <v>5.098234988699556</v>
+        <v>4.667676081306539</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2493,22 +2457,18 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>w1118</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>L6</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="n">
-        <v>0.002482599999998624</v>
+        <v>0.009930399999994496</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -2521,38 +2481,38 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>..\data\csvs\nSybxRalRNAi\N2\N2_nSybxRalRNAi_L7_FA.csv</t>
+          <t>..\data\csvs\graph 1\w1118\N2\L4.csv</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>5402</v>
       </c>
       <c r="C32" t="n">
-        <v>54.09107737874861</v>
+        <v>19.58533876342096</v>
       </c>
       <c r="D32" t="n">
-        <v>97.40000000000001</v>
+        <v>63.63333333333333</v>
       </c>
       <c r="E32" t="n">
-        <v>113</v>
+        <v>3000</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>67.95863427939746</v>
+        <v>91.86838434544181</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8224118710697556</v>
+        <v>0.6345962538252946</v>
       </c>
       <c r="J32" t="n">
-        <v>0.6007495318351138</v>
+        <v>0.2418677324490273</v>
       </c>
       <c r="K32" t="n">
-        <v>4.158004329002184</v>
+        <v>7.858396783059604</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2561,48 +2521,48 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>w1118</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>L7</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="n">
-        <v>0.002482600000011854</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S32" t="b">
-        <v>0</v>
-      </c>
-      <c r="T32" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>..\data\csvs\nSybxRalRNAi\N2\N2_nSybxRalRNAi_L8_FA.csv</t>
+          <t>..\data\csvs\graph 1\w1118\N2\L5.csv</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5401</v>
+        <v>5402</v>
       </c>
       <c r="C33" t="n">
-        <v>25.01388631734864</v>
+        <v>18.82636060718253</v>
       </c>
       <c r="D33" t="n">
-        <v>45.03333333333333</v>
+        <v>33.9</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>552</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -2611,16 +2571,16 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>111.3886815264712</v>
+        <v>140.2645039652821</v>
       </c>
       <c r="I33" t="n">
-        <v>0.825509003407642</v>
+        <v>0.9598392150908905</v>
       </c>
       <c r="J33" t="n">
-        <v>0.61846584384272</v>
+        <v>0.7805767098754526</v>
       </c>
       <c r="K33" t="n">
-        <v>4.272762572388041</v>
+        <v>6.162572514786268</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2629,48 +2589,48 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>w1118</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>L8</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="n">
-        <v>0.004965199999988428</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
       <c r="S33" t="b">
-        <v>0</v>
-      </c>
-      <c r="T33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>..\data\csvs\nSybxRalRNAi\N2\N2_nSybxRalRNAi_L9_FA.csv</t>
+          <t>..\data\csvs\graph 1\w1118\N2\L6.csv</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>5402</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.4627915586819696</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1666666666666667</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="E34" t="n">
-        <v>5</v>
+        <v>619</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -2679,16 +2639,16 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>94.57955518017006</v>
+        <v>170.4654493420507</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5258314780217016</v>
+        <v>0.9512580878462649</v>
       </c>
       <c r="J34" t="n">
-        <v>0.4013710789368652</v>
+        <v>0.7022819946431617</v>
       </c>
       <c r="K34" t="n">
-        <v>3.294267748681114</v>
+        <v>6.176285291338115</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2697,22 +2657,18 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>w1118</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>L9</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="n">
-        <v>0.007447800000000282</v>
+        <v>0.004965200000006068</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -2725,7 +2681,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>..\data\csvs\nSybxRalRNAi\N3\N3_nSybxRalRNAi_L1_FA.csv</t>
+          <t>..\data\csvs\graph 1\w1118\N2\L7.csv</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2735,10 +2691,10 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -2747,40 +2703,36 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>87.21447328052088</v>
+        <v>115.8963837202041</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4844351413470888</v>
+        <v>0.6437495855593633</v>
       </c>
       <c r="J35" t="n">
-        <v>0.3710795063056035</v>
+        <v>0.4992995093126965</v>
       </c>
       <c r="K35" t="n">
-        <v>3.142133033466354</v>
+        <v>3.495482799271124</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>w1118</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="n">
-        <v>0.007447800000000282</v>
+        <v>0.009930399999994496</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -2793,20 +2745,20 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>..\data\csvs\nSybxRalRNAi\N3\N3_nSybxRalRNAi_L2_FA.csv</t>
+          <t>..\data\csvs\graph 1\w1118\N2\L8.csv</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>5402</v>
       </c>
       <c r="C36" t="n">
-        <v>27.78600518326546</v>
+        <v>66.27175120325805</v>
       </c>
       <c r="D36" t="n">
-        <v>50.03333333333333</v>
+        <v>114.9</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -2815,66 +2767,66 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>72.04662166194157</v>
+        <v>59.14733167253873</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5542047820149353</v>
+        <v>0.9744206206349049</v>
       </c>
       <c r="J36" t="n">
-        <v>0.4242640687118441</v>
+        <v>0.7505997601919673</v>
       </c>
       <c r="K36" t="n">
-        <v>3.012573650552031</v>
+        <v>5.818840090602191</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>w1118</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+          <t>L8</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="n">
-        <v>0.007021853179890999</v>
+        <v>0.002482600000011854</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
       <c r="S36" t="b">
-        <v>0</v>
-      </c>
-      <c r="T36" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>..\data\csvs\nSybxRalRNAi\N3\N3_nSybxRalRNAi_L3_FA.csv</t>
+          <t>..\data\csvs\graph 1\w1118\N2\L9.csv</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>5402</v>
       </c>
       <c r="C37" t="n">
-        <v>38.68937430581266</v>
+        <v>31.7660125879304</v>
       </c>
       <c r="D37" t="n">
-        <v>52.16666666666666</v>
+        <v>57.2</v>
       </c>
       <c r="E37" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -2883,37 +2835,33 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>68.68420079634333</v>
+        <v>76.83317638397237</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6227035430312178</v>
+        <v>0.6255075417962472</v>
       </c>
       <c r="J37" t="n">
-        <v>0.4459820624195625</v>
+        <v>0.4846648326421237</v>
       </c>
       <c r="K37" t="n">
-        <v>3.947708195903186</v>
+        <v>4.053109917088262</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>w1118</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="n">
         <v>0.004965200000023708</v>
@@ -2922,9 +2870,3621 @@
         <v>0</v>
       </c>
       <c r="S37" t="b">
-        <v>0</v>
-      </c>
-      <c r="T37" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 1\w1118\N3\L1.csv</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>5403</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>128.0759402786976</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.7112695683748478</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.5383281573000747</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.04811067042385</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>w1118</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="n">
+        <v>0.009930399999994496</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 1\w1118\N3\L2.csv</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>168.2533117796777</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.9345675529328517</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.6926037828369134</v>
+      </c>
+      <c r="K39" t="n">
+        <v>5.923917622654734</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>w1118</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="n">
+        <v>0.00555126236092804</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 1\w1118\N3\L3.csv</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.259163272861903</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="E40" t="n">
+        <v>7</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>89.07019638398789</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.4960285672024571</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.3911521443121955</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.314287253694279</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>w1118</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="n">
+        <v>0.0121889165769408</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 1\w1118\N3\L4.csv</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>5403</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="E41" t="n">
+        <v>7</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>138.3586807545094</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.7689441316478843</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.6007495318351138</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.842460149435594</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>w1118</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="n">
+        <v>0.009930399999994496</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 1\w1118\N3\L5.csv</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>160.2800929634732</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.8902800942240687</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.6356886030125805</v>
+      </c>
+      <c r="K42" t="n">
+        <v>5.187918657804837</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>w1118</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="n">
+        <v>0.009930399999994496</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 1\w1118\N3\L6.csv</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>5403</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>39.86666666666667</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1231</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>90.97448298050858</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.5052266733460307</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.3088689042295113</v>
+      </c>
+      <c r="K43" t="n">
+        <v>4.131404119666846</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>w1118</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="n">
+        <v>0.009930399999994496</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 1\w1118\N3\L7.csv</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>140.3972966895168</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.7799849816084269</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.6155485358605313</v>
+      </c>
+      <c r="K44" t="n">
+        <v>4.295346318983022</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>w1118</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="n">
+        <v>0.004965199999997248</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 1\w1118\N3\L8.csv</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>5401</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>117.50070759014</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.6527817088341109</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.4695742752750054</v>
+      </c>
+      <c r="K45" t="n">
+        <v>4.434016238129797</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>w1118</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="n">
+        <v>0.007447800000000282</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 1\w1118\N3\L9.csv</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C46" t="n">
+        <v>37.81932617549056</v>
+      </c>
+      <c r="D46" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="E46" t="n">
+        <v>63</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>70.28835880477602</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.6279484110015726</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.3794733192201974</v>
+      </c>
+      <c r="K46" t="n">
+        <v>7.124226273778676</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>w1118</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="n">
+        <v>0.005551262360943818</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxRalRNAi\N1\L1.csv</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>113.9853976782455</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.6331349621083807</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.5028916384273823</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3.760664834839667</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="n">
+        <v>0.008951141596470501</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxRalRNAi\N1\L2.csv</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>5403</v>
+      </c>
+      <c r="C48" t="n">
+        <v>45.41921154913937</v>
+      </c>
+      <c r="D48" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1764</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>82.06135600235709</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.8362230570892366</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.5026080727192619</v>
+      </c>
+      <c r="K48" t="n">
+        <v>5.589105474044938</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="n">
+        <v>0.004965200000006068</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxRalRNAi\N1\L3.csv</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>5403</v>
+      </c>
+      <c r="C49" t="n">
+        <v>21.09938922820655</v>
+      </c>
+      <c r="D49" t="n">
+        <v>38</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>87.16689580927807</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.6139955093398315</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.4743416490252165</v>
+      </c>
+      <c r="K49" t="n">
+        <v>3.891336531321556</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="n">
+        <v>0.008951141596460717</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxRalRNAi\N1\L4.csv</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>68.98411020482557</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.3832450566934754</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.276586333718905</v>
+      </c>
+      <c r="K50" t="n">
+        <v>2.675556016980429</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="n">
+        <v>0.01279888697242365</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxRalRNAi\N1\L5.csv</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>5403</v>
+      </c>
+      <c r="C51" t="n">
+        <v>19.23005737553211</v>
+      </c>
+      <c r="D51" t="n">
+        <v>34.63333333333333</v>
+      </c>
+      <c r="E51" t="n">
+        <v>5</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>93.82556110788447</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.6457368279964519</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.5239274758971829</v>
+      </c>
+      <c r="K51" t="n">
+        <v>3.833079701754197</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="n">
+        <v>0.007447800000000282</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxRalRNAi\N1\L6.csv</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>5403</v>
+      </c>
+      <c r="C52" t="n">
+        <v>19.78530446048492</v>
+      </c>
+      <c r="D52" t="n">
+        <v>35.63333333333333</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>85.3292753092116</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.5907865818777632</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.4509988913511996</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3.872208672062936</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="n">
+        <v>0.007447800000000282</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxRalRNAi\N2\L1.csv</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>17</v>
+      </c>
+      <c r="F53" t="n">
+        <v>17</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>143.5257002386665</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.7972173684799103</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.6007495318348902</v>
+      </c>
+      <c r="K53" t="n">
+        <v>4.718400152594072</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="n">
+        <v>0.002482600000011854</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxRalRNAi\N2\L2.csv</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C54" t="n">
+        <v>5.553498704183636</v>
+      </c>
+      <c r="D54" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2406</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>191.3971388592535</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1.125644808033249</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.9940824915464667</v>
+      </c>
+      <c r="K54" t="n">
+        <v>5.846383497513595</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="n">
+        <v>0.007447800000000282</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>high untracked %; unusually fast median speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxRalRNAi\N2\L3.csv</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>5404</v>
+      </c>
+      <c r="C55" t="n">
+        <v>62.76831976313841</v>
+      </c>
+      <c r="D55" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="E55" t="n">
+        <v>13</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>64.07607585567288</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.9558837770612564</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.7648529270386402</v>
+      </c>
+      <c r="K55" t="n">
+        <v>6.413267497929511</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="n">
+        <v>0.004965199999988428</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxRalRNAi\N2\L4.csv</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C56" t="n">
+        <v>23.43576453165494</v>
+      </c>
+      <c r="D56" t="n">
+        <v>46.46666666666667</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1560</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1108</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>108.1588545972435</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.7847075303306662</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.5578778251181412</v>
+      </c>
+      <c r="K56" t="n">
+        <v>4.323019777886758</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxRalRNAi\N2\L5.csv</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>106.2824328467211</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.590348636437999</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.4589117562233681</v>
+      </c>
+      <c r="K57" t="n">
+        <v>4.384928733742462</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="n">
+        <v>0.004965199999997248</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxRalRNAi\N2\L6.csv</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>25.03333333333333</v>
+      </c>
+      <c r="E58" t="n">
+        <v>764</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>137.9499304505509</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.7662466049836191</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.7096110185096127</v>
+      </c>
+      <c r="K58" t="n">
+        <v>5.098234988699556</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="n">
+        <v>0.002482599999998624</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxRalRNAi\N2\L7.csv</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C59" t="n">
+        <v>54.09107737874861</v>
+      </c>
+      <c r="D59" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="E59" t="n">
+        <v>113</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>67.95863632516547</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.822411895826932</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.6007495318351138</v>
+      </c>
+      <c r="K59" t="n">
+        <v>4.158004329002184</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="n">
+        <v>0.002482600000011854</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxRalRNAi\N2\L8.csv</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>5401</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>45.03333333333333</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1352</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>135.8547811718065</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.7547487842878138</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.5432721647535967</v>
+      </c>
+      <c r="K60" t="n">
+        <v>4.272762572388041</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="n">
+        <v>0.004965199999988428</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxRalRNAi\N2\L9.csv</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="E61" t="n">
+        <v>5</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>94.57955518017006</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.5258314780217016</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.4013710789368652</v>
+      </c>
+      <c r="K61" t="n">
+        <v>3.294267748681114</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="n">
+        <v>0.007447800000000282</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxRalRNAi\N3\L1.csv</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>87.21447328052088</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.4844351413470888</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.3710795063056035</v>
+      </c>
+      <c r="K62" t="n">
+        <v>3.142133033466354</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="n">
+        <v>0.007447800000000282</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxRalRNAi\N3\L2.csv</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C63" t="n">
+        <v>27.78600518326546</v>
+      </c>
+      <c r="D63" t="n">
+        <v>50.03333333333333</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>72.04662166194157</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.5542047820149353</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.4242640687118441</v>
+      </c>
+      <c r="K63" t="n">
+        <v>3.012573650552031</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="n">
+        <v>0.007021853179890999</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxRalRNAi\N3\L3.csv</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>52.16666666666666</v>
+      </c>
+      <c r="E64" t="n">
+        <v>2133</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>82.99041328572496</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.4609724863121178</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.2954657340538655</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3.947708195903186</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="n">
+        <v>0.004965200000023708</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxRalRNAi\N3\L4.csv</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C65" t="n">
+        <v>8.885597926693817</v>
+      </c>
+      <c r="D65" t="n">
+        <v>16</v>
+      </c>
+      <c r="E65" t="n">
+        <v>199</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>98.39960678454833</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.5998756763943203</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.4368065933571307</v>
+      </c>
+      <c r="K65" t="n">
+        <v>4.066743168679471</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="n">
+        <v>0.004965199999988428</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxRalRNAi\N3\L5.csv</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C66" t="n">
+        <v>67.23435764531655</v>
+      </c>
+      <c r="D66" t="n">
+        <v>121.0666666666667</v>
+      </c>
+      <c r="E66" t="n">
+        <v>43</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>60.54832765965331</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1.026822967659468</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.7788452991447722</v>
+      </c>
+      <c r="K66" t="n">
+        <v>4.867494221876451</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="n">
+        <v>0.004965199999988428</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxRalRNAi\N3\L6.csv</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>96.12146896467311</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.5339092888243276</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.4036087214123323</v>
+      </c>
+      <c r="K67" t="n">
+        <v>3.359598190260246</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="n">
+        <v>0.007021853179903473</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxRalRNAi\N3\L7.csv</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C68" t="n">
+        <v>61.75490559052203</v>
+      </c>
+      <c r="D68" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="E68" t="n">
+        <v>9</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>56.82435616453033</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.8267365106381717</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.5247856705360969</v>
+      </c>
+      <c r="K68" t="n">
+        <v>4.861481255749085</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="n">
+        <v>0.00555126236092804</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxRalRNAi\N3\L8.csv</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.3146982599037393</v>
+      </c>
+      <c r="D69" t="n">
+        <v>48.06666666666667</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1888</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>56.30407895032964</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.3137300090100091</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.1529705854078451</v>
+      </c>
+      <c r="K69" t="n">
+        <v>4.107809635316745</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="n">
+        <v>0.004965200000006068</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxRalRNAi\N3\L9.csv</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>27.36666666666667</v>
+      </c>
+      <c r="E70" t="n">
+        <v>821</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>134.6302846591051</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.7478075430055833</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.4809365862563981</v>
+      </c>
+      <c r="K70" t="n">
+        <v>4.202677717836586</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>nSybxRalRNAi</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="n">
+        <v>0.007447800000000282</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxw1118\N1\L1.csv</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E71" t="n">
+        <v>72</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>128.8045483916092</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.715448333965613</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.5135172830590208</v>
+      </c>
+      <c r="K71" t="n">
+        <v>5.748191019790593</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>nSybxw1118</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="n">
+        <v>0.01837820000003826</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxw1118\N1\L2.csv</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C72" t="n">
+        <v>49.3891151425398</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E72" t="n">
+        <v>922</v>
+      </c>
+      <c r="F72" t="n">
+        <v>3584</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>37.79215705486608</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.4148425582312413</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.218403296678375</v>
+      </c>
+      <c r="K72" t="n">
+        <v>4.350413773424386</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>nSybxw1118</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="n">
+        <v>0.0158955999999877</v>
+      </c>
+      <c r="R72" t="n">
+        <v>5</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxw1118\N1\L3.csv</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0.1480932987782303</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>110.3868267280775</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.6140561471986509</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.4242640687118893</v>
+      </c>
+      <c r="K73" t="n">
+        <v>5.345811444486316</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>nSybxw1118</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="n">
+        <v>0.0126588258444367</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+      <c r="T73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxw1118\N1\L4.csv</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>29.03333333333333</v>
+      </c>
+      <c r="E74" t="n">
+        <v>2868</v>
+      </c>
+      <c r="F74" t="n">
+        <v>340</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>122.9457212147936</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.6835381090518544</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.2107130530619556</v>
+      </c>
+      <c r="K74" t="n">
+        <v>5.675077091987356</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>nSybxw1118</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="n">
+        <v>0.004965199999988428</v>
+      </c>
+      <c r="R74" t="n">
+        <v>13</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxw1118\N1\L5.csv</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>8</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>108.910923847972</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.6052848676248906</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.4676527280687236</v>
+      </c>
+      <c r="K75" t="n">
+        <v>6.189095248903584</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>nSybxw1118</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="n">
+        <v>0.01710633027573655</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="b">
+        <v>0</v>
+      </c>
+      <c r="T75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxw1118\N2\L1.csv</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>5403</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>105.2191771478721</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.584334563945976</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.426380112106463</v>
+      </c>
+      <c r="K76" t="n">
+        <v>4.052221612893405</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>nSybxw1118</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="n">
+        <v>0.007447800000000282</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxw1118\N2\L2.csv</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" t="n">
+        <v>62.56666666666667</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1920</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>206.8881251522565</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1.149591360357047</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.9823486154550725</v>
+      </c>
+      <c r="K77" t="n">
+        <v>6.44190189307443</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>nSybxw1118</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="n">
+        <v>0.002482599999994214</v>
+      </c>
+      <c r="R77" t="n">
+        <v>1</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>unusually fast median speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxw1118\N2\L3.csv</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C78" t="n">
+        <v>24.21325435024065</v>
+      </c>
+      <c r="D78" t="n">
+        <v>48.03333333333333</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1442</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>78.57035075670409</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.5758882293430547</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.2735867749724712</v>
+      </c>
+      <c r="K78" t="n">
+        <v>4.268126052496738</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>nSybxw1118</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="n">
+        <v>0.007447800000000282</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxw1118\N2\L4.csv</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>5401</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="E79" t="n">
+        <v>276</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>198.4299717536092</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1.103410408268448</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.8275868534479027</v>
+      </c>
+      <c r="K79" t="n">
+        <v>5.726464878090107</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>nSybxw1118</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="n">
+        <v>0.002482599999976574</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="b">
+        <v>0</v>
+      </c>
+      <c r="T79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxw1118\N2\L6.csv</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>5401</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" t="n">
+        <v>7.766666666666667</v>
+      </c>
+      <c r="E80" t="n">
+        <v>853</v>
+      </c>
+      <c r="F80" t="n">
+        <v>575</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>111.6697016144829</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.6203872311915716</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.3899999999997962</v>
+      </c>
+      <c r="K80" t="n">
+        <v>5.037142046835727</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>nSybxw1118</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="n">
+        <v>0.007447799999995872</v>
+      </c>
+      <c r="R80" t="n">
+        <v>20</v>
+      </c>
+      <c r="S80" t="b">
+        <v>0</v>
+      </c>
+      <c r="T80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxw1118\N2\L7.csv</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C81" t="n">
+        <v>4.313217326915957</v>
+      </c>
+      <c r="D81" t="n">
+        <v>7.766666666666667</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>108.461571829191</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.6296143875533532</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.4657252408878</v>
+      </c>
+      <c r="K81" t="n">
+        <v>3.394775397577987</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>nSybxw1118</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="n">
+        <v>0.004965199999988428</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="b">
+        <v>0</v>
+      </c>
+      <c r="T81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxw1118\N2\L8.csv</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C82" t="n">
+        <v>13.12476860422066</v>
+      </c>
+      <c r="D82" t="n">
+        <v>60.26666666666667</v>
+      </c>
+      <c r="E82" t="n">
+        <v>2492</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>89.48670771772406</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.5721656503690796</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.3595623577524373</v>
+      </c>
+      <c r="K82" t="n">
+        <v>5.249999999999957</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>nSybxw1118</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxw1118\N2\L9.csv</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0.1480932987782303</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="E83" t="n">
+        <v>2</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>74.68419659581954</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.4154507505793782</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.3088689042296562</v>
+      </c>
+      <c r="K83" t="n">
+        <v>3.403645104883809</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>nSybxw1118</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="n">
+        <v>0.007850670519138035</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="b">
+        <v>0</v>
+      </c>
+      <c r="T83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxw1118\N3\L1.csv</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C84" t="n">
+        <v>34.89448352462051</v>
+      </c>
+      <c r="D84" t="n">
+        <v>62.83333333333334</v>
+      </c>
+      <c r="E84" t="n">
+        <v>5</v>
+      </c>
+      <c r="F84" t="n">
+        <v>2</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>80.52028163573186</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.6870331197588044</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.4719579621500334</v>
+      </c>
+      <c r="K84" t="n">
+        <v>5.272921391411036</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>nSybxw1118</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="n">
+        <v>0.009930399999994496</v>
+      </c>
+      <c r="R84" t="n">
+        <v>1</v>
+      </c>
+      <c r="S84" t="b">
+        <v>1</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxw1118\N3\L2.csv</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>162.850693501779</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.9045585641646677</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.7003570517955996</v>
+      </c>
+      <c r="K85" t="n">
+        <v>6.024699162613728</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>nSybxw1118</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="n">
+        <v>0.004965199999988428</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="b">
+        <v>0</v>
+      </c>
+      <c r="T85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxw1118\N3\L3.csv</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C86" t="n">
+        <v>6.460570159200296</v>
+      </c>
+      <c r="D86" t="n">
+        <v>11.63333333333333</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1292</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>79.71017195643083</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.4733383132804682</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0.3088689042295527</v>
+      </c>
+      <c r="K86" t="n">
+        <v>4.697371605483276</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>nSybxw1118</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="n">
+        <v>0.004965199999988428</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="b">
+        <v>1</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxw1118\N3\L4.csv</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>5403</v>
+      </c>
+      <c r="C87" t="n">
+        <v>24.04219877845641</v>
+      </c>
+      <c r="D87" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>108.2655374238604</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.7916076341008558</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.5770615218503026</v>
+      </c>
+      <c r="K87" t="n">
+        <v>4.867864007960829</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>nSybxw1118</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="n">
+        <v>0.007447800000000282</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="b">
+        <v>1</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxw1118\N3\L5.csv</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="n">
+        <v>70.03333333333333</v>
+      </c>
+      <c r="E88" t="n">
+        <v>2549</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>76.98182978812399</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.4275976474067247</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0.1637508927598055</v>
+      </c>
+      <c r="K88" t="n">
+        <v>3.195387300469311</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>nSybxw1118</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="b">
+        <v>0</v>
+      </c>
+      <c r="T88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxw1118\N3\L6.csv</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>71.26991664115283</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.3958706719560423</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0.3059411708154812</v>
+      </c>
+      <c r="K89" t="n">
+        <v>3.501785258978633</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>nSybxw1118</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="n">
+        <v>0.01117622584444016</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="b">
+        <v>0</v>
+      </c>
+      <c r="T89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxw1118\N3\L7.csv</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>5403</v>
+      </c>
+      <c r="C90" t="n">
+        <v>33.48139922265408</v>
+      </c>
+      <c r="D90" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E90" t="n">
+        <v>2339</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1817</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>29.80484699893915</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.2489268958708727</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.07269073201435233</v>
+      </c>
+      <c r="K90" t="n">
+        <v>3.180438296069147</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>nSybxw1118</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>283</v>
+      </c>
+      <c r="S90" t="b">
+        <v>1</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxw1118\N3\L8.csv</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C91" t="n">
+        <v>48.00074046649389</v>
+      </c>
+      <c r="D91" t="n">
+        <v>86.43333333333334</v>
+      </c>
+      <c r="E91" t="n">
+        <v>2</v>
+      </c>
+      <c r="F91" t="n">
+        <v>2</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>94.41699785323205</v>
+      </c>
+      <c r="I91" t="n">
+        <v>1.008728609543077</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0.75538069872102</v>
+      </c>
+      <c r="K91" t="n">
+        <v>6.484933612878095</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>nSybxw1118</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="n">
+        <v>0.004965199999988428</v>
+      </c>
+      <c r="R91" t="n">
+        <v>1</v>
+      </c>
+      <c r="S91" t="b">
+        <v>1</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>high untracked %</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 2\nSybxw1118\N3\L9.csv</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>5401</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
+        <v>75.53333333333333</v>
+      </c>
+      <c r="E92" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>80.25007699704958</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.4458337610947199</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0.1533876182349029</v>
+      </c>
+      <c r="K92" t="n">
+        <v>3.396763165132372</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>nSybxw1118</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="n">
+        <v>0.004965199999988428</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="b">
+        <v>0</v>
+      </c>
+      <c r="T92" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/results/larva_batch_summary.xlsx
+++ b/data/results/larva_batch_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T92"/>
+  <dimension ref="A1:T95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,20 +521,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\RalG0501\N1\L1.csv</t>
+          <t>..\data\csvs\graph 3\nSybxCazIR\N1\L1.csv</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>5402</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3517215845982969</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>7.033333333333333</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>794</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -543,16 +543,16 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>98.28030882272476</v>
+        <v>100.9835559169196</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5478278083763921</v>
+        <v>0.5609158817825567</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3900000000000421</v>
+        <v>0.4242640687117838</v>
       </c>
       <c r="K2" t="n">
-        <v>3.812833591962552</v>
+        <v>4.661694970716148</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>RalG0501</t>
+          <t>nSybxCazIR</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -572,7 +572,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>0.01241299999998871</v>
+        <v>0.01421874103826837</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -585,38 +585,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\RalG0501\N1\L2.csv</t>
+          <t>..\data\csvs\graph 3\nSybxCazIR\N1\L2.csv</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5403</v>
+        <v>5402</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2220988339811216</v>
+        <v>78.30433172898927</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1666666666666667</v>
+        <v>141</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>104.7843791721658</v>
+        <v>62.26721221404198</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5832154684907185</v>
+        <v>1.595231739044628</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4509988913511996</v>
+        <v>1.341640786500217</v>
       </c>
       <c r="K3" t="n">
-        <v>4.443748417721254</v>
+        <v>7.072941396618441</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>RalG0501</t>
+          <t>nSybxCazIR</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -636,51 +636,55 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>0.01824614369812799</v>
+        <v>0.009930400000012135</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S3" t="b">
-        <v>0</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>unusually fast median speed</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\RalG0501\N1\L3.csv</t>
+          <t>..\data\csvs\graph 3\nSybxCazIR\N1\L3.csv</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>5402</v>
       </c>
       <c r="C4" t="n">
-        <v>19.71492039985191</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>22.03333333333333</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>409</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>78.63007562022435</v>
+        <v>103.0755818484886</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5440272759701869</v>
+        <v>0.5725360961774963</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4297665493272367</v>
+        <v>0.420000000000087</v>
       </c>
       <c r="K4" t="n">
-        <v>3.07467071407653</v>
+        <v>3.33216146067383</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -689,7 +693,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>RalG0501</t>
+          <t>nSybxCazIR</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -700,37 +704,33 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>0.01336921015018389</v>
+        <v>0.01489559999998292</v>
       </c>
       <c r="R4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S4" t="b">
-        <v>1</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\RalG0501\N1\L4.csv</t>
+          <t>..\data\csvs\graph 3\nSybxCazIR\N1\L4.csv</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>5402</v>
       </c>
       <c r="C5" t="n">
-        <v>12.45834875971862</v>
+        <v>0.3702332469455757</v>
       </c>
       <c r="D5" t="n">
-        <v>20.93333333333333</v>
+        <v>3.733333333333333</v>
       </c>
       <c r="E5" t="n">
-        <v>1432</v>
+        <v>131</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -739,16 +739,16 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>61.42067522566082</v>
+        <v>115.8955559219192</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3897250966095229</v>
+        <v>0.6461376468421439</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2418677324488687</v>
+        <v>0.4500000000000171</v>
       </c>
       <c r="K5" t="n">
-        <v>4.263801121065659</v>
+        <v>4.667676081306386</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>RalG0501</t>
+          <t>nSybxCazIR</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -768,55 +768,51 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>0.01241300000000635</v>
+        <v>0.01489560000000056</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\RalG0501\N1\L5.csv</t>
+          <t>..\data\csvs\graph 3\nSybxCazIR\N1\L5.csv</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>5402</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1851166234727878</v>
+        <v>51.11069974083673</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1</v>
+        <v>92.03333333333333</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>100.7494620368079</v>
+        <v>69.12771767979828</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5606536562983189</v>
+        <v>0.7870328388591833</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4295346318982424</v>
+        <v>0.5977457653551949</v>
       </c>
       <c r="K6" t="n">
-        <v>3.712371209887228</v>
+        <v>4.452246623896826</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -825,7 +821,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>RalG0501</t>
+          <t>nSybxCazIR</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -836,10 +832,10 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>0.01689560000000301</v>
+        <v>0.007447800000000282</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S6" t="b">
         <v>0</v>
@@ -849,20 +845,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\RalG0501\N1\L6.csv</t>
+          <t>..\data\csvs\graph 3\nSybxCazIR\N1\L6.csv</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5402</v>
+        <v>5401</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>3.266666666666667</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>277</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -871,16 +867,16 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>123.4994085479989</v>
+        <v>126.9355369207178</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6859807917867002</v>
+        <v>0.7053280436416995</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5161395160225938</v>
+        <v>0.5307541803885919</v>
       </c>
       <c r="K7" t="n">
-        <v>4.902407571795773</v>
+        <v>4.620389593962722</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -889,7 +885,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>RalG0501</t>
+          <t>nSybxCazIR</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -900,7 +896,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="n">
-        <v>0.0174243183126165</v>
+        <v>0.01447592117414853</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -913,7 +909,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\RalG0501\N2\L1.csv</t>
+          <t>..\data\csvs\graph 3\nSybxCazIR\N2\L1.csv</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -935,16 +931,16 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>123.764500379386</v>
+        <v>94.02676499252775</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6874532515055692</v>
+        <v>0.5222741991808615</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5316013544001889</v>
+        <v>0.3911521443123263</v>
       </c>
       <c r="K8" t="n">
-        <v>4.956631920972262</v>
+        <v>4.089364253768861</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -953,7 +949,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>RalG0501</t>
+          <t>nSybxCazIR</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -964,7 +960,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>0.01510106625771797</v>
+        <v>0.01053277976984274</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -977,20 +973,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\RalG0501\N2\L2.csv</t>
+          <t>..\data\csvs\graph 3\nSybxCazIR\N2\L2.csv</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>5403</v>
       </c>
       <c r="C9" t="n">
-        <v>50.06477882657783</v>
+        <v>0.1480658893207477</v>
       </c>
       <c r="D9" t="n">
-        <v>90.16666666666667</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E9" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -999,16 +995,16 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>64.79859693700487</v>
+        <v>104.2771424982118</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7207852829477739</v>
+        <v>0.5799618603904992</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5307541803885919</v>
+        <v>0.4429446918069226</v>
       </c>
       <c r="K9" t="n">
-        <v>4.443647150708517</v>
+        <v>4.050000000000153</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1017,7 +1013,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>RalG0501</t>
+          <t>nSybxCazIR</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1028,28 +1024,24 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="n">
-        <v>0.007447800000000282</v>
+        <v>0.01023602202617091</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="b">
-        <v>1</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\RalG0501\N2\L3.csv</t>
+          <t>..\data\csvs\graph 3\nSybxCazIR\N2\L3.csv</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5402</v>
+        <v>5403</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -1067,16 +1059,16 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>89.59403194659993</v>
+        <v>103.7796346467932</v>
       </c>
       <c r="I10" t="n">
-        <v>0.49765246406184</v>
+        <v>0.5763400665316171</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3899999999999601</v>
+        <v>0.424264068711814</v>
       </c>
       <c r="K10" t="n">
-        <v>3.747238983571816</v>
+        <v>3.690975480818004</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1085,7 +1077,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>RalG0501</t>
+          <t>nSybxCazIR</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1096,7 +1088,7 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
-        <v>0.01361846625772432</v>
+        <v>0.009930399999994496</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1109,7 +1101,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\RalG0501\N2\L4.csv</t>
+          <t>..\data\csvs\graph 3\nSybxCazIR\N2\L4.csv</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1131,16 +1123,16 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>130.6870617837222</v>
+        <v>87.68051045137184</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7259048053159906</v>
+        <v>0.4870237573673681</v>
       </c>
       <c r="J11" t="n">
-        <v>0.540832691319615</v>
+        <v>0.3758989225843267</v>
       </c>
       <c r="K11" t="n">
-        <v>5.022917478916028</v>
+        <v>3.394775397577859</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1149,7 +1141,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>RalG0501</t>
+          <t>nSybxCazIR</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1160,7 +1152,7 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
-        <v>0.01404370635979448</v>
+        <v>0.009930400000012135</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1173,20 +1165,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\RalG0501\N2\L6.csv</t>
+          <t>..\data\csvs\graph 3\nSybxCazIR\N2\L5.csv</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5403</v>
+        <v>5402</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>8.459829692706405</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>15.23333333333333</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -1195,16 +1187,16 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>121.9151474211305</v>
+        <v>120.4187523865152</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6771809706783773</v>
+        <v>0.7311399659169109</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5108815909776654</v>
+        <v>0.5408326913194849</v>
       </c>
       <c r="K12" t="n">
-        <v>5.312965273743102</v>
+        <v>4.548142477979316</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1213,18 +1205,18 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>RalG0501</t>
+          <t>nSybxCazIR</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>L6</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="n">
-        <v>0.01053277976984274</v>
+        <v>0.009930399999994496</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
@@ -1237,20 +1229,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\RalG0501\N2\L7.csv</t>
+          <t>..\data\csvs\graph 3\nSybxCazIR\N2\L6.csv</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>5402</v>
       </c>
       <c r="C13" t="n">
-        <v>51.96223620881155</v>
+        <v>22.43613476490189</v>
       </c>
       <c r="D13" t="n">
-        <v>93.13333333333334</v>
+        <v>67.36666666666666</v>
       </c>
       <c r="E13" t="n">
-        <v>25</v>
+        <v>2030</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1259,16 +1251,16 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>64.79782078763523</v>
+        <v>76.77946249192583</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7493965395640159</v>
+        <v>0.5498648543226963</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5515432893254391</v>
+        <v>0.0948683298050325</v>
       </c>
       <c r="K13" t="n">
-        <v>5.021125371866523</v>
+        <v>5.425605956941594</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1277,48 +1269,44 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>RalG0501</t>
+          <t>nSybxCazIR</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>L7</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="n">
-        <v>0.009930399999976856</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="b">
-        <v>1</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\RalG0501\N2\L8.csv</t>
+          <t>..\data\csvs\graph 3\nSybxCazIR\N2\L7.csv</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5402</v>
+        <v>5403</v>
       </c>
       <c r="C14" t="n">
-        <v>9.422436134764903</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>16.96666666666667</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1327,16 +1315,16 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>146.5473183456619</v>
+        <v>144.8097576039462</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8986957380150976</v>
+        <v>0.8042008012066617</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6579513659837346</v>
+        <v>0.5770615218500643</v>
       </c>
       <c r="K14" t="n">
-        <v>5.508983572311538</v>
+        <v>5.373602143813872</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1345,12 +1333,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>RalG0501</t>
+          <t>nSybxCazIR</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>L8</t>
+          <t>L7</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -1362,31 +1350,27 @@
         <v>0</v>
       </c>
       <c r="S14" t="b">
-        <v>1</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\RalG0501\N2\L9.csv</t>
+          <t>..\data\csvs\graph 3\nSybxCazIR\N2\L8.csv</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5402</v>
+        <v>5403</v>
       </c>
       <c r="C15" t="n">
-        <v>52.85079600148093</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>95.16666666666667</v>
+        <v>3.1</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>226</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1395,16 +1379,16 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>70.59684698774427</v>
+        <v>106.6924633520077</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8318560132098696</v>
+        <v>0.5929555206669564</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6184658438425261</v>
+        <v>0.4326661530557345</v>
       </c>
       <c r="K15" t="n">
-        <v>4.669218350002479</v>
+        <v>4.255032314801119</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1413,35 +1397,31 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>RalG0501</t>
+          <t>nSybxCazIR</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>L9</t>
+          <t>L8</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="n">
-        <v>0.007447800000000282</v>
+        <v>0.009930399999994496</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="b">
-        <v>1</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\RalG0501\N3\L1.csv</t>
+          <t>..\data\csvs\graph 3\nSybxCazIR\N2\L9.csv</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1463,36 +1443,36 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>80.13809826004909</v>
+        <v>156.9619778524874</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4451292256621872</v>
+        <v>0.8718495344518833</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3600000000000136</v>
+        <v>0.6328506932918194</v>
       </c>
       <c r="K16" t="n">
-        <v>3.026879581351042</v>
+        <v>5.510943657850431</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>RalG0501</t>
+          <t>nSybxCazIR</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L9</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="n">
-        <v>0.01110252472187975</v>
+        <v>0.007447800000000282</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -1505,7 +1485,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\RalG0501\N3\L2.csv</t>
+          <t>..\data\csvs\graph 3\nSybxCazIR\N3\L1.csv</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1527,16 +1507,16 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>123.9421683358477</v>
+        <v>87.37975157728296</v>
       </c>
       <c r="I17" t="n">
-        <v>0.688440112956014</v>
+        <v>0.4853531840989611</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5366563145999381</v>
+        <v>0.3710795063056035</v>
       </c>
       <c r="K17" t="n">
-        <v>4.118859065323702</v>
+        <v>3.649657518178872</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1545,18 +1525,18 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>RalG0501</t>
+          <t>nSybxCazIR</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="n">
-        <v>0.009930399999985677</v>
+        <v>0.007447800000000282</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -1569,17 +1549,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\RalG0501\N3\L4.csv</t>
+          <t>..\data\csvs\graph 3\nSybxCazIR\N3\L2.csv</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>5402</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>54.7945205479452</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>98.66666666666667</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -1591,16 +1571,16 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>88.81815490888393</v>
+        <v>66.98438751364895</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4933428341541415</v>
+        <v>0.8232411410935964</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3661966684720482</v>
+        <v>0.5977457653552964</v>
       </c>
       <c r="K18" t="n">
-        <v>3.260214716855346</v>
+        <v>4.628271815699754</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1609,18 +1589,18 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>RalG0501</t>
+          <t>nSybxCazIR</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="n">
-        <v>0.009930399999994496</v>
+        <v>0.004965200000006068</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -1633,7 +1613,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\RalG0501\N3\L5.csv</t>
+          <t>..\data\csvs\graph 3\nSybxCazIR\N3\L3.csv</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1655,16 +1635,16 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>113.4658016968247</v>
+        <v>95.17716883858398</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6302488522319464</v>
+        <v>0.5286641483350341</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4589117562233681</v>
+        <v>0.3911521443121302</v>
       </c>
       <c r="K19" t="n">
-        <v>4.041435388571684</v>
+        <v>4.553679830642639</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1673,12 +1653,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>RalG0501</t>
+          <t>nSybxCazIR</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>L5</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
@@ -1697,7 +1677,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\RalG0501\N3\L6.csv</t>
+          <t>..\data\csvs\graph 3\nSybxCazIR\N3\L4.csv</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1707,10 +1687,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1719,16 +1699,16 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>109.7828852516609</v>
+        <v>92.14431332574128</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6097919936215196</v>
+        <v>0.5122923276079019</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4569463863517212</v>
+        <v>0.3794733192201974</v>
       </c>
       <c r="K20" t="n">
-        <v>5.08382729840426</v>
+        <v>4.534765705083258</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1737,18 +1717,18 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>RalG0501</t>
+          <t>nSybxCazIR</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>L6</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="n">
-        <v>0.007447800000000282</v>
+        <v>0.009930400000012135</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -1761,7 +1741,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\RalG0501\N3\L7.csv</t>
+          <t>..\data\csvs\graph 3\nSybxCazIR\N3\L5.csv</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1771,10 +1751,10 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.03333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1783,16 +1763,16 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>132.3046362178633</v>
+        <v>90.03195963949655</v>
       </c>
       <c r="I21" t="n">
-        <v>0.734889666087002</v>
+        <v>0.5000849452295679</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5531726674376251</v>
+        <v>0.3231098884281683</v>
       </c>
       <c r="K21" t="n">
-        <v>4.966789707648112</v>
+        <v>4.172696969586935</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1801,18 +1781,18 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>RalG0501</t>
+          <t>nSybxCazIR</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>L7</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="n">
-        <v>0.007447800000000282</v>
+        <v>0.008951141596470501</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -1825,20 +1805,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\RalG0501\N3\L8.csv</t>
+          <t>..\data\csvs\graph 3\nSybxCazIR\N3\L6.csv</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5402</v>
+        <v>5401</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>17.05239770412886</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>30.7</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>388</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1847,16 +1827,16 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>114.926143996528</v>
+        <v>100.3824556560157</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6383603628764749</v>
+        <v>0.6723540231481291</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4883646178830577</v>
+        <v>0.4589117562233158</v>
       </c>
       <c r="K22" t="n">
-        <v>4.318020379757135</v>
+        <v>4.838284820057601</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1865,18 +1845,18 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>RalG0501</t>
+          <t>nSybxCazIR</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>L8</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="n">
-        <v>0.009930400000012135</v>
+        <v>0.0035109265899455</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -1889,20 +1869,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\RalG0501\N3\L9.csv</t>
+          <t>..\data\csvs\graph 3\nSybxCazIR\N3\L7.csv</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>5402</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>5.94224361347649</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1911,16 +1891,16 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>133.2462151855279</v>
+        <v>115.218320396486</v>
       </c>
       <c r="I23" t="n">
-        <v>0.74011969182852</v>
+        <v>0.6804231519477523</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5580322571323375</v>
+        <v>0.4837354648978961</v>
       </c>
       <c r="K23" t="n">
-        <v>4.295136784783468</v>
+        <v>4.157138438878322</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1929,18 +1909,18 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>RalG0501</t>
+          <t>nSybxCazIR</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>L9</t>
+          <t>L7</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="n">
-        <v>0.007447800000000282</v>
+        <v>0.003510926589939263</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -1953,17 +1933,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\w1118\N1\L2.csv</t>
+          <t>..\data\csvs\graph 3\nSybxCazIR\N3\L8.csv</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5402</v>
+        <v>5401</v>
       </c>
       <c r="C24" t="n">
-        <v>60.71825249907442</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>109.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -1975,107 +1955,103 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>72.60225832679761</v>
+        <v>158.0739728252512</v>
       </c>
       <c r="I24" t="n">
-        <v>1.026906058370546</v>
+        <v>0.8781887379180622</v>
       </c>
       <c r="J24" t="n">
-        <v>0.745184540902613</v>
+        <v>0.6708203932498987</v>
       </c>
       <c r="K24" t="n">
-        <v>6.294926528562629</v>
+        <v>5.809862304736565</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>N1</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>w1118</t>
+          <t>nSybxCazIR</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L8</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="n">
-        <v>0.007447800000000282</v>
+        <v>0.009930400000012135</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="b">
-        <v>1</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\w1118\N1\L4.csv</t>
+          <t>..\data\csvs\graph 3\nSybxCazIR\N3\L9.csv</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>5402</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6479081821547575</v>
+        <v>22.78785634950018</v>
       </c>
       <c r="D25" t="n">
-        <v>43.7</v>
+        <v>41.03333333333333</v>
       </c>
       <c r="E25" t="n">
-        <v>1357</v>
+        <v>886</v>
       </c>
       <c r="F25" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>120.3520936519898</v>
+        <v>138.1400527012421</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6728592638016575</v>
+        <v>0.9938133287859142</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4242640687120024</v>
+        <v>0.5916924876995824</v>
       </c>
       <c r="K25" t="n">
-        <v>5.035891182303321</v>
+        <v>5.648451115128632</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>N1</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>w1118</t>
+          <t>nSybxCazIR</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>L9</t>
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="n">
-        <v>0.004965200000014888</v>
+        <v>0.007447800000000282</v>
       </c>
       <c r="R25" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="S25" t="b">
         <v>0</v>
@@ -2085,38 +2061,38 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\w1118\N1\L5.csv</t>
+          <t>..\data\csvs\graph 3\nSybxSmnIR\N1\L1.csv</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5403</v>
+        <v>5402</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1295576531556543</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>93.66666666666667</v>
+        <v>0.3</v>
       </c>
       <c r="E26" t="n">
-        <v>3166</v>
+        <v>1460</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1451</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>86.98132157917314</v>
+        <v>81.27752566272838</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4836774137859489</v>
+        <v>0.4514582058659232</v>
       </c>
       <c r="J26" t="n">
-        <v>0.05685600988223756</v>
+        <v>0.3053659174084327</v>
       </c>
       <c r="K26" t="n">
-        <v>6.033655608335696</v>
+        <v>3.277148150450298</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2125,21 +2101,21 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>w1118</t>
+          <t>nSybxSmnIR</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>L5</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="n">
-        <v>0.002482599999994214</v>
+        <v>0.01489560000000056</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S26" t="b">
         <v>0</v>
@@ -2149,20 +2125,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\w1118\N1\L6.csv</t>
+          <t>..\data\csvs\graph 3\nSybxSmnIR\N1\L2.csv</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5402</v>
+        <v>5403</v>
       </c>
       <c r="C27" t="n">
-        <v>1.018141429100333</v>
+        <v>41.16231723116787</v>
       </c>
       <c r="D27" t="n">
-        <v>7.966666666666667</v>
+        <v>74.13333333333334</v>
       </c>
       <c r="E27" t="n">
-        <v>1738</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2171,16 +2147,16 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>111.9394488620525</v>
+        <v>69.64976589284133</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6281675020317199</v>
+        <v>0.6576937289220145</v>
       </c>
       <c r="J27" t="n">
-        <v>0.4576431721886614</v>
+        <v>0.4883646178830577</v>
       </c>
       <c r="K27" t="n">
-        <v>3.570504166080656</v>
+        <v>3.599124893637186</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2189,18 +2165,18 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>w1118</t>
+          <t>nSybxSmnIR</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>L6</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="n">
-        <v>0.004965199999988428</v>
+        <v>0.01023602202616236</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -2213,20 +2189,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\w1118\N1\L7.csv</t>
+          <t>..\data\csvs\graph 3\nSybxSmnIR\N1\L3.csv</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>5402</v>
       </c>
       <c r="C28" t="n">
-        <v>59.21880784894483</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>105.9333333333333</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>365</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -2235,16 +2211,16 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>66.79612448464449</v>
+        <v>93.09938488525241</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9100289439324863</v>
+        <v>0.5171230413918853</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6113183007860086</v>
+        <v>0.3899999999999437</v>
       </c>
       <c r="K28" t="n">
-        <v>5.344043412997553</v>
+        <v>4.458811500837337</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2253,45 +2229,41 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>w1118</t>
+          <t>nSybxSmnIR</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>L7</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="n">
-        <v>0.005551262360951707</v>
+        <v>0.01528148697242904</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="b">
-        <v>1</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\w1118\N2\L1.csv</t>
+          <t>..\data\csvs\graph 3\nSybxSmnIR\N1\L4.csv</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5402</v>
+        <v>5403</v>
       </c>
       <c r="C29" t="n">
-        <v>15.66086634579785</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>28.2</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -2303,134 +2275,126 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>88.13771131337786</v>
+        <v>98.80282159426338</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5804898659497993</v>
+        <v>0.5487013416934287</v>
       </c>
       <c r="J29" t="n">
-        <v>0.436806593356955</v>
+        <v>0.3900000000000421</v>
       </c>
       <c r="K29" t="n">
-        <v>4.053998026640029</v>
+        <v>5.304573498406826</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>N1</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>w1118</t>
+          <t>nSybxSmnIR</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="n">
-        <v>0.01053277976984274</v>
+        <v>0.01421874103827395</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
       <c r="S29" t="b">
-        <v>1</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\w1118\N2\L2.csv</t>
+          <t>..\data\csvs\graph 3\nSybxSmnIR\N1\L5.csv</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5402</v>
+        <v>5403</v>
       </c>
       <c r="C30" t="n">
-        <v>65.69788967049242</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>118.3</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>60.56791913616659</v>
+        <v>125.4660570782104</v>
       </c>
       <c r="I30" t="n">
-        <v>0.9811218002618779</v>
+        <v>0.6971627546483259</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7130918594403068</v>
+        <v>0.4429446918071175</v>
       </c>
       <c r="K30" t="n">
-        <v>5.616733926402641</v>
+        <v>9.52366526081212</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>N1</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>w1118</t>
+          <t>nSybxSmnIR</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="n">
-        <v>0.004965200000006068</v>
+        <v>0.01524860144463909</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S30" t="b">
-        <v>1</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\w1118\N2\L3.csv</t>
+          <t>..\data\csvs\graph 3\nSybxSmnIR\N1\L6.csv</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5401</v>
+        <v>5402</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.7034431691965939</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1.266666666666667</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -2439,36 +2403,36 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>137.2630290393675</v>
+        <v>114.0388131572689</v>
       </c>
       <c r="I31" t="n">
-        <v>0.7625723835520416</v>
+        <v>0.6379198945959477</v>
       </c>
       <c r="J31" t="n">
-        <v>0.5531726674375326</v>
+        <v>0.4743416490253041</v>
       </c>
       <c r="K31" t="n">
-        <v>4.667676081306539</v>
+        <v>5.20696648731289</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>N1</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>w1118</t>
+          <t>nSybxSmnIR</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="n">
-        <v>0.009930399999994496</v>
+        <v>0.01589560000000705</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -2481,38 +2445,38 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\w1118\N2\L4.csv</t>
+          <t>..\data\csvs\graph 3\nSybxSmnIR\N2\L1.csv</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>5402</v>
       </c>
       <c r="C32" t="n">
-        <v>19.58533876342096</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>63.63333333333333</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>91.86838434544181</v>
+        <v>76.29667669983975</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6345962538252946</v>
+        <v>0.4237919461201986</v>
       </c>
       <c r="J32" t="n">
-        <v>0.2418677324490273</v>
+        <v>0.3189043743818978</v>
       </c>
       <c r="K32" t="n">
-        <v>7.858396783059604</v>
+        <v>3.194401352366614</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2521,48 +2485,44 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>w1118</t>
+          <t>nSybxSmnIR</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>0.008951141596460717</v>
       </c>
       <c r="R32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S32" t="b">
-        <v>1</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\w1118\N2\L5.csv</t>
+          <t>..\data\csvs\graph 3\nSybxSmnIR\N2\L2.csv</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>5402</v>
       </c>
       <c r="C33" t="n">
-        <v>18.82636060718253</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>33.9</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>552</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -2571,16 +2531,16 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>140.2645039652821</v>
+        <v>85.42968136979206</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9598392150908905</v>
+        <v>0.4745214665976231</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7805767098754526</v>
+        <v>0.3600000000000136</v>
       </c>
       <c r="K33" t="n">
-        <v>6.162572514786268</v>
+        <v>2.805601539777207</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2589,48 +2549,44 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>w1118</t>
+          <t>nSybxSmnIR</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>L5</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>0.007447800000000282</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
       <c r="S33" t="b">
-        <v>1</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\w1118\N2\L6.csv</t>
+          <t>..\data\csvs\graph 3\nSybxSmnIR\N2\L3.csv</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5402</v>
+        <v>5403</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4627915586819696</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>2.833333333333333</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>619</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -2639,16 +2595,16 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>170.4654493420507</v>
+        <v>89.77585938475613</v>
       </c>
       <c r="I34" t="n">
-        <v>0.9512580878462649</v>
+        <v>0.4985701187602155</v>
       </c>
       <c r="J34" t="n">
-        <v>0.7022819946431617</v>
+        <v>0.3612478373637766</v>
       </c>
       <c r="K34" t="n">
-        <v>6.176285291338115</v>
+        <v>4.387185886191749</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2657,18 +2613,18 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>w1118</t>
+          <t>nSybxSmnIR</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>L6</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="n">
-        <v>0.004965200000006068</v>
+        <v>0.009930400000012135</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -2681,20 +2637,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\w1118\N2\L7.csv</t>
+          <t>..\data\csvs\graph 3\nSybxSmnIR\N2\L4.csv</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5402</v>
+        <v>5401</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -2703,16 +2659,16 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>115.8963837202041</v>
+        <v>88.05142065613217</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6437495855593633</v>
+        <v>0.4891745592007343</v>
       </c>
       <c r="J35" t="n">
-        <v>0.4992995093126965</v>
+        <v>0.3649657518179538</v>
       </c>
       <c r="K35" t="n">
-        <v>3.495482799271124</v>
+        <v>3.529305880764521</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2721,18 +2677,18 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>w1118</t>
+          <t>nSybxSmnIR</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>L7</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="n">
-        <v>0.009930399999994496</v>
+        <v>0.007850670519138035</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -2745,20 +2701,20 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\w1118\N2\L8.csv</t>
+          <t>..\data\csvs\graph 3\nSybxSmnIR\N2\L5.csv</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>5402</v>
       </c>
       <c r="C36" t="n">
-        <v>66.27175120325805</v>
+        <v>61.75490559052203</v>
       </c>
       <c r="D36" t="n">
-        <v>114.9</v>
+        <v>111.2</v>
       </c>
       <c r="E36" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -2767,16 +2723,16 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>59.14733167253873</v>
+        <v>57.09902764087546</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9744206206349049</v>
+        <v>0.829525825291169</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7505997601919673</v>
+        <v>0.6328506932918802</v>
       </c>
       <c r="K36" t="n">
-        <v>5.818840090602191</v>
+        <v>4.727451744862172</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2785,48 +2741,44 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>w1118</t>
+          <t>nSybxSmnIR</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>L8</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="n">
-        <v>0.002482600000011854</v>
+        <v>0.005551262360933958</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
       <c r="S36" t="b">
-        <v>1</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\w1118\N2\L9.csv</t>
+          <t>..\data\csvs\graph 3\nSybxSmnIR\N2\L6.csv</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5402</v>
+        <v>5401</v>
       </c>
       <c r="C37" t="n">
-        <v>31.7660125879304</v>
+        <v>45.49157563414182</v>
       </c>
       <c r="D37" t="n">
-        <v>57.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -2835,16 +2787,16 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>76.83317638397237</v>
+        <v>62.33827562026456</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6255075417962472</v>
+        <v>0.635456428341127</v>
       </c>
       <c r="J37" t="n">
-        <v>0.4846648326421237</v>
+        <v>0.4883646178830577</v>
       </c>
       <c r="K37" t="n">
-        <v>4.053109917088262</v>
+        <v>3.283321488980329</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2853,35 +2805,31 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>w1118</t>
+          <t>nSybxSmnIR</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>L9</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="n">
-        <v>0.004965200000023708</v>
+        <v>0.005551262360943818</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
       <c r="S37" t="b">
-        <v>1</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\w1118\N3\L1.csv</t>
+          <t>..\data\csvs\graph 3\nSybxSmnIR\N2\L8.csv</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -2903,36 +2851,36 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>128.0759402786976</v>
+        <v>94.24821258031633</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7112695683748478</v>
+        <v>0.5234073264364106</v>
       </c>
       <c r="J38" t="n">
-        <v>0.5383281573000747</v>
+        <v>0.4036087214123323</v>
       </c>
       <c r="K38" t="n">
-        <v>4.04811067042385</v>
+        <v>3.338637446623703</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>w1118</t>
+          <t>nSybxSmnIR</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L8</t>
         </is>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="n">
-        <v>0.009930399999994496</v>
+        <v>0.008951141596460717</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -2945,7 +2893,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\w1118\N3\L2.csv</t>
+          <t>..\data\csvs\graph 3\nSybxSmnIR\N2\L9.csv</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2967,30 +2915,30 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>168.2533117796777</v>
+        <v>127.7859221926237</v>
       </c>
       <c r="I39" t="n">
-        <v>0.9345675529328517</v>
+        <v>0.7097903473021129</v>
       </c>
       <c r="J39" t="n">
-        <v>0.6926037828369134</v>
+        <v>0.5692099788303299</v>
       </c>
       <c r="K39" t="n">
-        <v>5.923917622654734</v>
+        <v>5.891697548245279</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>w1118</t>
+          <t>nSybxSmnIR</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L9</t>
         </is>
       </c>
       <c r="O39" t="inlineStr"/>
@@ -3009,20 +2957,20 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\w1118\N3\L3.csv</t>
+          <t>..\data\csvs\graph 3\nSybxSmnIR\N3\L1.csv</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>5402</v>
       </c>
       <c r="C40" t="n">
-        <v>0.259163272861903</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0.4666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -3031,16 +2979,16 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>89.07019638398789</v>
+        <v>97.25667603546091</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4960285672024571</v>
+        <v>0.540214827080879</v>
       </c>
       <c r="J40" t="n">
-        <v>0.3911521443121955</v>
+        <v>0.4002499219239437</v>
       </c>
       <c r="K40" t="n">
-        <v>3.314287253694279</v>
+        <v>3.023011743278737</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -3049,18 +2997,18 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>w1118</t>
+          <t>nSybxSmnIR</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="n">
-        <v>0.0121889165769408</v>
+        <v>0.009930399999994496</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -3073,20 +3021,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\w1118\N3\L4.csv</t>
+          <t>..\data\csvs\graph 3\nSybxSmnIR\N3\L2.csv</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>5403</v>
+        <v>5402</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -3095,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>138.3586807545094</v>
+        <v>93.89104847496034</v>
       </c>
       <c r="I41" t="n">
-        <v>0.7689441316478843</v>
+        <v>0.5215203581279041</v>
       </c>
       <c r="J41" t="n">
-        <v>0.6007495318351138</v>
+        <v>0.3649657518179187</v>
       </c>
       <c r="K41" t="n">
-        <v>3.842460149435594</v>
+        <v>4.40581434016464</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -3113,18 +3061,18 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>w1118</t>
+          <t>nSybxSmnIR</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="n">
-        <v>0.009930399999994496</v>
+        <v>0.008951141596470501</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3137,20 +3085,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\w1118\N3\L5.csv</t>
+          <t>..\data\csvs\graph 3\nSybxSmnIR\N3\L3.csv</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>5402</v>
+        <v>5403</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0.03333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -3159,16 +3107,16 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>160.2800929634732</v>
+        <v>83.85191666733289</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8902800942240687</v>
+        <v>0.4656715105553474</v>
       </c>
       <c r="J42" t="n">
-        <v>0.6356886030125805</v>
+        <v>0.3420526275297108</v>
       </c>
       <c r="K42" t="n">
-        <v>5.187918657804837</v>
+        <v>2.64612924854381</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -3177,18 +3125,18 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>w1118</t>
+          <t>nSybxSmnIR</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>L5</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="n">
-        <v>0.009930399999994496</v>
+        <v>0.007447800000000282</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -3201,7 +3149,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\w1118\N3\L6.csv</t>
+          <t>..\data\csvs\graph 3\nSybxSmnIR\N3\L4.csv</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -3211,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>39.86666666666667</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1231</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -3223,16 +3171,16 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>90.97448298050858</v>
+        <v>86.495540227726</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5052266733460307</v>
+        <v>0.4803528705723398</v>
       </c>
       <c r="J43" t="n">
-        <v>0.3088689042295113</v>
+        <v>0.363728565512818</v>
       </c>
       <c r="K43" t="n">
-        <v>4.131404119666846</v>
+        <v>2.906905571221767</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3241,18 +3189,18 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>w1118</t>
+          <t>nSybxSmnIR</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>L6</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="n">
-        <v>0.009930399999994496</v>
+        <v>0.004965200000006068</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -3265,7 +3213,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\w1118\N3\L7.csv</t>
+          <t>..\data\csvs\graph 3\nSybxSmnIR\N3\L5.csv</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -3275,10 +3223,10 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0.03333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -3287,16 +3235,16 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>140.3972966895168</v>
+        <v>74.07092348652901</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7799849816084269</v>
+        <v>0.4114289399362841</v>
       </c>
       <c r="J44" t="n">
-        <v>0.6155485358605313</v>
+        <v>0.3014962686335604</v>
       </c>
       <c r="K44" t="n">
-        <v>4.295346318983022</v>
+        <v>2.673200329193465</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -3305,18 +3253,18 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>w1118</t>
+          <t>nSybxSmnIR</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>L7</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="n">
-        <v>0.004965199999997248</v>
+        <v>0.007850670519132456</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -3329,11 +3277,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\w1118\N3\L8.csv</t>
+          <t>..\data\csvs\graph 3\nSybxSmnIR\N3\L6.csv</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>5401</v>
+        <v>5402</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -3351,16 +3299,16 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>117.50070759014</v>
+        <v>125.9556700623914</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6527817088341109</v>
+        <v>0.6996241625387414</v>
       </c>
       <c r="J45" t="n">
-        <v>0.4695742752750054</v>
+        <v>0.5307541803885919</v>
       </c>
       <c r="K45" t="n">
-        <v>4.434016238129797</v>
+        <v>3.784521105767487</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -3369,18 +3317,18 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>w1118</t>
+          <t>nSybxSmnIR</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>L8</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="n">
-        <v>0.007447800000000282</v>
+        <v>0.004965200000006068</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -3393,38 +3341,38 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 1\w1118\N3\L9.csv</t>
+          <t>..\data\csvs\graph 3\nSybxSmnIR\N3\L7.csv</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>5402</v>
       </c>
       <c r="C46" t="n">
-        <v>37.81932617549056</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>68.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>70.28835880477602</v>
+        <v>118.5847998154185</v>
       </c>
       <c r="I46" t="n">
-        <v>0.6279484110015726</v>
+        <v>0.6586824651846983</v>
       </c>
       <c r="J46" t="n">
-        <v>0.3794733192201974</v>
+        <v>0.4080441152621937</v>
       </c>
       <c r="K46" t="n">
-        <v>7.124226273778676</v>
+        <v>7.439576600855884</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3433,39 +3381,35 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>w1118</t>
+          <t>nSybxSmnIR</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>L9</t>
+          <t>L7</t>
         </is>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="n">
-        <v>0.005551262360943818</v>
+        <v>0.01110252472186003</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S46" t="b">
-        <v>1</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxRalRNAi\N1\L1.csv</t>
+          <t>..\data\csvs\graph 3\nSybxSmnIR\N3\L8.csv</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>5402</v>
+        <v>5403</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
@@ -3483,36 +3427,36 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>113.9853976782455</v>
+        <v>102.267153843385</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6331349621083807</v>
+        <v>0.567940506349787</v>
       </c>
       <c r="J47" t="n">
-        <v>0.5028916384273823</v>
+        <v>0.4024922359499774</v>
       </c>
       <c r="K47" t="n">
-        <v>3.760664834839667</v>
+        <v>3.96181776461275</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>N1</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>nSybxSmnIR</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L8</t>
         </is>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="n">
-        <v>0.008951141596470501</v>
+        <v>0.007447800000000282</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -3525,20 +3469,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxRalRNAi\N1\L2.csv</t>
+          <t>..\data\csvs\graph 3\nSybxSmnIR\N3\L9.csv</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>5403</v>
+        <v>5402</v>
       </c>
       <c r="C48" t="n">
-        <v>45.41921154913937</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>81.8</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E48" t="n">
-        <v>1764</v>
+        <v>5</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -3547,66 +3491,62 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>82.06135600235709</v>
+        <v>93.40902176615847</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8362230570892366</v>
+        <v>0.5193236940297914</v>
       </c>
       <c r="J48" t="n">
-        <v>0.5026080727192619</v>
+        <v>0.3911521443121302</v>
       </c>
       <c r="K48" t="n">
-        <v>5.589105474044938</v>
+        <v>3.902537635949269</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>N1</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>nSybxSmnIR</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L9</t>
         </is>
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="n">
-        <v>0.004965200000006068</v>
+        <v>0.01241300000000988</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
       <c r="S48" t="b">
-        <v>1</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxRalRNAi\N1\L3.csv</t>
+          <t>..\data\csvs\graph 3\nSybxTbphIR\N1\L1.csv</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>5403</v>
       </c>
       <c r="C49" t="n">
-        <v>21.09938922820655</v>
+        <v>12.04886174347585</v>
       </c>
       <c r="D49" t="n">
-        <v>38</v>
+        <v>21.7</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -3615,16 +3555,16 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>87.16689580927807</v>
+        <v>107.8684653213251</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6139955093398315</v>
+        <v>0.681131121793255</v>
       </c>
       <c r="J49" t="n">
-        <v>0.4743416490252165</v>
+        <v>0.5307541803886703</v>
       </c>
       <c r="K49" t="n">
-        <v>3.891336531321556</v>
+        <v>3.872324883064397</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3633,35 +3573,31 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>nSybxTbphIR</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="n">
-        <v>0.008951141596460717</v>
+        <v>0.007447800000000282</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
       <c r="S49" t="b">
-        <v>1</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxRalRNAi\N1\L4.csv</t>
+          <t>..\data\csvs\graph 3\nSybxTbphIR\N1\L2.csv</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -3674,25 +3610,25 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>68.98411020482557</v>
+        <v>87.04654788608329</v>
       </c>
       <c r="I50" t="n">
-        <v>0.3832450566934754</v>
+        <v>0.4835023952198664</v>
       </c>
       <c r="J50" t="n">
-        <v>0.276586333718905</v>
+        <v>0.3841874542458413</v>
       </c>
       <c r="K50" t="n">
-        <v>2.675556016980429</v>
+        <v>4.217321424790886</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3701,21 +3637,21 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>nSybxTbphIR</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="n">
-        <v>0.01279888697242365</v>
+        <v>0.01222711946407236</v>
       </c>
       <c r="R50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" t="b">
         <v>0</v>
@@ -3725,20 +3661,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxRalRNAi\N1\L5.csv</t>
+          <t>..\data\csvs\graph 3\nSybxTbphIR\N1\L3.csv</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>5403</v>
+        <v>5402</v>
       </c>
       <c r="C51" t="n">
-        <v>19.23005737553211</v>
+        <v>13.12476860422066</v>
       </c>
       <c r="D51" t="n">
-        <v>34.63333333333333</v>
+        <v>23.63333333333333</v>
       </c>
       <c r="E51" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -3747,16 +3683,16 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>93.82556110788447</v>
+        <v>113.2743422139059</v>
       </c>
       <c r="I51" t="n">
-        <v>0.6457368279964519</v>
+        <v>0.7242605000889123</v>
       </c>
       <c r="J51" t="n">
-        <v>0.5239274758971829</v>
+        <v>0.5474486277268605</v>
       </c>
       <c r="K51" t="n">
-        <v>3.833079701754197</v>
+        <v>4.370743643820876</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3765,45 +3701,41 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>nSybxTbphIR</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>L5</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="n">
-        <v>0.007447800000000282</v>
+        <v>0.01053277976984274</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
       <c r="S51" t="b">
-        <v>1</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxRalRNAi\N1\L6.csv</t>
+          <t>..\data\csvs\graph 3\nSybxTbphIR\N1\L4.csv</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>5403</v>
+        <v>5402</v>
       </c>
       <c r="C52" t="n">
-        <v>19.78530446048492</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>35.63333333333333</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -3815,16 +3747,16 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>85.3292753092116</v>
+        <v>132.6593016824442</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5907865818777632</v>
+        <v>0.7368596649645112</v>
       </c>
       <c r="J52" t="n">
-        <v>0.4509988913511996</v>
+        <v>0.5707889277131605</v>
       </c>
       <c r="K52" t="n">
-        <v>3.872208672062936</v>
+        <v>4.201071291944508</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3833,35 +3765,31 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>nSybxTbphIR</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>L6</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="n">
-        <v>0.007447800000000282</v>
+        <v>0.01241299999999577</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
       <c r="S52" t="b">
-        <v>1</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxRalRNAi\N2\L1.csv</t>
+          <t>..\data\csvs\graph 3\nSybxTbphIR\N1\L5.csv</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -3874,45 +3802,45 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F53" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>143.5257002386665</v>
+        <v>160.9258680401749</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7972173684799103</v>
+        <v>0.8943638460921168</v>
       </c>
       <c r="J53" t="n">
-        <v>0.6007495318348902</v>
+        <v>0.7224956747275355</v>
       </c>
       <c r="K53" t="n">
-        <v>4.718400152594072</v>
+        <v>4.362396130568652</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>N1</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>nSybxTbphIR</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="n">
-        <v>0.002482600000011854</v>
+        <v>0.009930399999994496</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -3925,88 +3853,84 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxRalRNAi\N2\L2.csv</t>
+          <t>..\data\csvs\graph 3\nSybxTbphIR\N1\L6.csv</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>5402</v>
       </c>
       <c r="C54" t="n">
-        <v>5.553498704183636</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>47.5</v>
+        <v>0.7</v>
       </c>
       <c r="E54" t="n">
-        <v>2406</v>
+        <v>30</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>191.3971388592535</v>
+        <v>126.1347436552252</v>
       </c>
       <c r="I54" t="n">
-        <v>1.125644808033249</v>
+        <v>0.7006188316342815</v>
       </c>
       <c r="J54" t="n">
-        <v>0.9940824915464667</v>
+        <v>0.5400000000000205</v>
       </c>
       <c r="K54" t="n">
-        <v>5.846383497513595</v>
+        <v>4.112517477166667</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>N1</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>nSybxTbphIR</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="n">
-        <v>0.007447800000000282</v>
+        <v>0.01241300000000635</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S54" t="b">
-        <v>1</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>high untracked %; unusually fast median speed</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxRalRNAi\N2\L3.csv</t>
+          <t>..\data\csvs\graph 3\nSybxTbphIR\N1\L7.csv</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>5404</v>
+        <v>5403</v>
       </c>
       <c r="C55" t="n">
-        <v>62.76831976313841</v>
+        <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>112.5</v>
+        <v>16.4</v>
       </c>
       <c r="E55" t="n">
-        <v>13</v>
+        <v>1025</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -4015,84 +3939,80 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>64.07607585567288</v>
+        <v>104.3847718754136</v>
       </c>
       <c r="I55" t="n">
-        <v>0.9558837770612564</v>
+        <v>0.5797006953466141</v>
       </c>
       <c r="J55" t="n">
-        <v>0.7648529270386402</v>
+        <v>0.4080441152621153</v>
       </c>
       <c r="K55" t="n">
-        <v>6.413267497929511</v>
+        <v>3.776307720512181</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>N1</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>nSybxTbphIR</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L7</t>
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="n">
-        <v>0.004965199999988428</v>
+        <v>0.002482600000003034</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
       <c r="S55" t="b">
-        <v>1</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxRalRNAi\N2\L4.csv</t>
+          <t>..\data\csvs\graph 3\nSybxTbphIR\N2\L1.csv</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>5402</v>
       </c>
       <c r="C56" t="n">
-        <v>23.43576453165494</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>46.46666666666667</v>
+        <v>61.76666666666667</v>
       </c>
       <c r="E56" t="n">
-        <v>1560</v>
+        <v>1853</v>
       </c>
       <c r="F56" t="n">
-        <v>1108</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>108.1588545972435</v>
+        <v>112.480025002727</v>
       </c>
       <c r="I56" t="n">
-        <v>0.7847075303306662</v>
+        <v>0.6247733290282931</v>
       </c>
       <c r="J56" t="n">
-        <v>0.5578778251181412</v>
+        <v>0.3088689042297598</v>
       </c>
       <c r="K56" t="n">
-        <v>4.323019777886758</v>
+        <v>5.736906832082828</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -4101,66 +4021,62 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>nSybxTbphIR</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>0.002482600000011854</v>
       </c>
       <c r="R56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S56" t="b">
-        <v>1</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxRalRNAi\N2\L5.csv</t>
+          <t>..\data\csvs\graph 3\nSybxTbphIR\N2\L2.csv</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>5402</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>47.57497223250648</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>85.66666666666667</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>106.2824328467211</v>
+        <v>75.18446114989227</v>
       </c>
       <c r="I57" t="n">
-        <v>0.590348636437999</v>
+        <v>0.7975720772619408</v>
       </c>
       <c r="J57" t="n">
-        <v>0.4589117562233681</v>
+        <v>0.6118823416310042</v>
       </c>
       <c r="K57" t="n">
-        <v>4.384928733742462</v>
+        <v>4.785916840062995</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -4169,21 +4085,21 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>nSybxTbphIR</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>L5</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="n">
-        <v>0.004965199999997248</v>
+        <v>0.004965199999988428</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S57" t="b">
         <v>0</v>
@@ -4193,20 +4109,20 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxRalRNAi\N2\L6.csv</t>
+          <t>..\data\csvs\graph 3\nSybxTbphIR\N2\L3.csv</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>5402</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>42.91003332099223</v>
       </c>
       <c r="D58" t="n">
-        <v>25.03333333333333</v>
+        <v>77.26666666666667</v>
       </c>
       <c r="E58" t="n">
-        <v>764</v>
+        <v>6</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -4215,16 +4131,16 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>137.9499304505509</v>
+        <v>87.22083442307049</v>
       </c>
       <c r="I58" t="n">
-        <v>0.7662466049836191</v>
+        <v>0.8487268999974421</v>
       </c>
       <c r="J58" t="n">
-        <v>0.7096110185096127</v>
+        <v>0.6462197768561287</v>
       </c>
       <c r="K58" t="n">
-        <v>5.098234988699556</v>
+        <v>4.31854142043357</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -4233,18 +4149,18 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>nSybxTbphIR</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>L6</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="n">
-        <v>0.002482599999998624</v>
+        <v>0.007447800000000282</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -4257,20 +4173,20 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxRalRNAi\N2\L7.csv</t>
+          <t>..\data\csvs\graph 3\nSybxTbphIR\N2\L4.csv</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>5402</v>
       </c>
       <c r="C59" t="n">
-        <v>54.09107737874861</v>
+        <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>97.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -4279,16 +4195,16 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>67.95863632516547</v>
+        <v>116.9205345634374</v>
       </c>
       <c r="I59" t="n">
-        <v>0.822411895826932</v>
+        <v>0.6494382590081693</v>
       </c>
       <c r="J59" t="n">
-        <v>0.6007495318351138</v>
+        <v>0.5099999999998772</v>
       </c>
       <c r="K59" t="n">
-        <v>4.158004329002184</v>
+        <v>4.271814602718971</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -4297,48 +4213,44 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>nSybxTbphIR</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>L7</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="n">
-        <v>0.002482600000011854</v>
+        <v>0.01110252472188764</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
       <c r="S59" t="b">
-        <v>1</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxRalRNAi\N2\L8.csv</t>
+          <t>..\data\csvs\graph 3\nSybxTbphIR\N2\L5.csv</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>5401</v>
+        <v>5402</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>48.00074046649389</v>
       </c>
       <c r="D60" t="n">
-        <v>45.03333333333333</v>
+        <v>86.43333333333334</v>
       </c>
       <c r="E60" t="n">
-        <v>1352</v>
+        <v>5</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -4347,16 +4259,16 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>135.8547811718065</v>
+        <v>74.57631778583027</v>
       </c>
       <c r="I60" t="n">
-        <v>0.7547487842878138</v>
+        <v>0.796755531899896</v>
       </c>
       <c r="J60" t="n">
-        <v>0.5432721647535967</v>
+        <v>0.6074537019394399</v>
       </c>
       <c r="K60" t="n">
-        <v>4.272762572388041</v>
+        <v>4.137825515896136</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -4365,18 +4277,18 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>nSybxTbphIR</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>L8</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="n">
-        <v>0.004965199999988428</v>
+        <v>0.004965200000023708</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -4389,7 +4301,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxRalRNAi\N2\L9.csv</t>
+          <t>..\data\csvs\graph 3\nSybxTbphIR\N2\L6.csv</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -4399,10 +4311,10 @@
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>0.1666666666666667</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="E61" t="n">
-        <v>5</v>
+        <v>183</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -4411,16 +4323,16 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>94.57955518017006</v>
+        <v>101.9702457716881</v>
       </c>
       <c r="I61" t="n">
-        <v>0.5258314780217016</v>
+        <v>0.566396477161756</v>
       </c>
       <c r="J61" t="n">
-        <v>0.4013710789368652</v>
+        <v>0.4242640687116934</v>
       </c>
       <c r="K61" t="n">
-        <v>3.294267748681114</v>
+        <v>5.167059124879522</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -4429,18 +4341,18 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>nSybxTbphIR</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>L9</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="n">
-        <v>0.007447800000000282</v>
+        <v>0.009930400000012135</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -4453,7 +4365,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxRalRNAi\N3\L1.csv</t>
+          <t>..\data\csvs\graph 3\nSybxTbphIR\N2\L7.csv</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -4463,10 +4375,10 @@
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>323</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -4475,36 +4387,36 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>87.21447328052088</v>
+        <v>150.4384993261927</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4844351413470888</v>
+        <v>0.8356146972386189</v>
       </c>
       <c r="J62" t="n">
-        <v>0.3710795063056035</v>
+        <v>0.666108099335344</v>
       </c>
       <c r="K62" t="n">
-        <v>3.142133033466354</v>
+        <v>4.518063744570277</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>nSybxTbphIR</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L7</t>
         </is>
       </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="n">
-        <v>0.007447800000000282</v>
+        <v>0.002482600000003034</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -4517,20 +4429,20 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxRalRNAi\N3\L2.csv</t>
+          <t>..\data\csvs\graph 3\nSybxTbphIR\N2\L8.csv</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>5402</v>
       </c>
       <c r="C63" t="n">
-        <v>27.78600518326546</v>
+        <v>1.295816364309515</v>
       </c>
       <c r="D63" t="n">
-        <v>50.03333333333333</v>
+        <v>56.06666666666667</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>1973</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -4539,30 +4451,30 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>72.04662166194157</v>
+        <v>86.86444055044544</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5542047820149353</v>
+        <v>0.4888263396198392</v>
       </c>
       <c r="J63" t="n">
-        <v>0.4242640687118441</v>
+        <v>0.2473863375368967</v>
       </c>
       <c r="K63" t="n">
-        <v>3.012573650552031</v>
+        <v>4.62603501932258</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>nSybxTbphIR</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L8</t>
         </is>
       </c>
       <c r="O63" t="inlineStr"/>
@@ -4574,31 +4486,27 @@
         <v>0</v>
       </c>
       <c r="S63" t="b">
-        <v>1</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxRalRNAi\N3\L3.csv</t>
+          <t>..\data\csvs\graph 3\nSybxTbphIR\N2\L9.csv</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>5402</v>
+        <v>5403</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>43.73496205811586</v>
       </c>
       <c r="D64" t="n">
-        <v>52.16666666666666</v>
+        <v>78.76666666666667</v>
       </c>
       <c r="E64" t="n">
-        <v>2133</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -4607,30 +4515,30 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>82.99041328572496</v>
+        <v>103.6696082666515</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4609724863121178</v>
+        <v>1.023728850559429</v>
       </c>
       <c r="J64" t="n">
-        <v>0.2954657340538655</v>
+        <v>0.8319254774316903</v>
       </c>
       <c r="K64" t="n">
-        <v>3.947708195903186</v>
+        <v>6.786633922645285</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>nSybxTbphIR</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L9</t>
         </is>
       </c>
       <c r="O64" t="inlineStr"/>
@@ -4649,20 +4557,20 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxRalRNAi\N3\L4.csv</t>
+          <t>..\data\csvs\graph 3\nSybxTbphIR\N3\L1.csv</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>5402</v>
       </c>
       <c r="C65" t="n">
-        <v>8.885597926693817</v>
+        <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -4671,16 +4579,16 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>98.39960678454833</v>
+        <v>105.2233037779794</v>
       </c>
       <c r="I65" t="n">
-        <v>0.5998756763943203</v>
+        <v>0.584465675493313</v>
       </c>
       <c r="J65" t="n">
-        <v>0.4368065933571307</v>
+        <v>0.424264068711814</v>
       </c>
       <c r="K65" t="n">
-        <v>4.066743168679471</v>
+        <v>4.244549446054377</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -4689,48 +4597,44 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>nSybxTbphIR</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="n">
-        <v>0.004965199999988428</v>
+        <v>0.007447800000000282</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
       <c r="S65" t="b">
-        <v>1</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxRalRNAi\N3\L5.csv</t>
+          <t>..\data\csvs\graph 3\nSybxTbphIR\N3\L2.csv</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>5402</v>
+        <v>5403</v>
       </c>
       <c r="C66" t="n">
-        <v>67.23435764531655</v>
+        <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>121.0666666666667</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -4739,16 +4643,16 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>60.54832765965331</v>
+        <v>103.4627596286638</v>
       </c>
       <c r="I66" t="n">
-        <v>1.026822967659468</v>
+        <v>0.5745803015290475</v>
       </c>
       <c r="J66" t="n">
-        <v>0.7788452991447722</v>
+        <v>0.4210700654286429</v>
       </c>
       <c r="K66" t="n">
-        <v>4.867494221876451</v>
+        <v>3.683286575872</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -4757,35 +4661,31 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>nSybxTbphIR</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>L5</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="n">
-        <v>0.004965199999988428</v>
+        <v>0.009930399999994496</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
       <c r="S66" t="b">
-        <v>1</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxRalRNAi\N3\L6.csv</t>
+          <t>..\data\csvs\graph 3\nSybxTbphIR\N3\L3.csv</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -4807,16 +4707,16 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>96.12146896467311</v>
+        <v>141.1713335140083</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5339092888243276</v>
+        <v>0.7841399750824385</v>
       </c>
       <c r="J67" t="n">
-        <v>0.4036087214123323</v>
+        <v>0.6264183905345206</v>
       </c>
       <c r="K67" t="n">
-        <v>3.359598190260246</v>
+        <v>4.540418482915372</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -4825,18 +4725,18 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>nSybxTbphIR</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>L6</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="n">
-        <v>0.007021853179903473</v>
+        <v>0.007447800000000282</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
@@ -4849,20 +4749,20 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxRalRNAi\N3\L7.csv</t>
+          <t>..\data\csvs\graph 3\nSybxTbphIR\N3\L4.csv</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>5402</v>
       </c>
       <c r="C68" t="n">
-        <v>61.75490559052203</v>
+        <v>6.701221769714921</v>
       </c>
       <c r="D68" t="n">
-        <v>111.2</v>
+        <v>12.06666666666667</v>
       </c>
       <c r="E68" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -4871,16 +4771,16 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>56.82435616453033</v>
+        <v>143.6929989126833</v>
       </c>
       <c r="I68" t="n">
-        <v>0.8267365106381717</v>
+        <v>0.8554852088470922</v>
       </c>
       <c r="J68" t="n">
-        <v>0.5247856705360969</v>
+        <v>0.6242595614006261</v>
       </c>
       <c r="K68" t="n">
-        <v>4.861481255749085</v>
+        <v>5.528878729001106</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -4889,48 +4789,44 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>nSybxTbphIR</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>L7</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="n">
-        <v>0.00555126236092804</v>
+        <v>0.009930399999994496</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
       <c r="S68" t="b">
-        <v>1</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxRalRNAi\N3\L8.csv</t>
+          <t>..\data\csvs\graph 3\nSybxTbphIR\N3\L5.csv</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>5402</v>
+        <v>5403</v>
       </c>
       <c r="C69" t="n">
-        <v>0.3146982599037393</v>
+        <v>36.36868406440866</v>
       </c>
       <c r="D69" t="n">
-        <v>48.06666666666667</v>
+        <v>65.5</v>
       </c>
       <c r="E69" t="n">
-        <v>1888</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -4939,16 +4835,16 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>56.30407895032964</v>
+        <v>70.06852250659782</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3137300090100091</v>
+        <v>0.6115960649397539</v>
       </c>
       <c r="J69" t="n">
-        <v>0.1529705854078451</v>
+        <v>0.4295346318981679</v>
       </c>
       <c r="K69" t="n">
-        <v>4.107809635316745</v>
+        <v>3.797696670351475</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4957,18 +4853,18 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>nSybxTbphIR</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>L8</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="n">
-        <v>0.004965200000006068</v>
+        <v>0.007447800000000282</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
@@ -4981,7 +4877,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxRalRNAi\N3\L9.csv</t>
+          <t>..\data\csvs\graph 3\nSybxTbphIR\N3\L6.csv</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -4991,10 +4887,10 @@
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>27.36666666666667</v>
+        <v>36.73333333333333</v>
       </c>
       <c r="E70" t="n">
-        <v>821</v>
+        <v>1103</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -5003,16 +4899,16 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>134.6302846591051</v>
+        <v>169.0695296989732</v>
       </c>
       <c r="I70" t="n">
-        <v>0.7478075430055833</v>
+        <v>0.9391012573540446</v>
       </c>
       <c r="J70" t="n">
-        <v>0.4809365862563981</v>
+        <v>0.9417960927250072</v>
       </c>
       <c r="K70" t="n">
-        <v>4.202677717836586</v>
+        <v>4.170431632337524</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -5021,44 +4917,48 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>nSybxRalRNAi</t>
+          <t>nSybxTbphIR</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>L9</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="n">
-        <v>0.007447800000000282</v>
+        <v>0.004965200000001658</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
       <c r="S70" t="b">
-        <v>0</v>
-      </c>
-      <c r="T70" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>unusually fast median speed</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxw1118\N1\L1.csv</t>
+          <t>..\data\csvs\graph 3\nSybxTbphIR\N3\L7.csv</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>5402</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>0.4813032210292484</v>
       </c>
       <c r="D71" t="n">
-        <v>1.3</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E71" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -5067,130 +4967,130 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>128.8045483916092</v>
+        <v>217.7088259257466</v>
       </c>
       <c r="I71" t="n">
-        <v>0.715448333965613</v>
+        <v>1.215119028422772</v>
       </c>
       <c r="J71" t="n">
-        <v>0.5135172830590208</v>
+        <v>0.971648084442217</v>
       </c>
       <c r="K71" t="n">
-        <v>5.748191019790593</v>
+        <v>5.238931188706403</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>N1</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>nSybxw1118</t>
+          <t>nSybxTbphIR</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L7</t>
         </is>
       </c>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="n">
-        <v>0.01837820000003826</v>
+        <v>0.004965199999988428</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
       <c r="S71" t="b">
-        <v>0</v>
-      </c>
-      <c r="T71" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>unusually fast median speed</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxw1118\N1\L2.csv</t>
+          <t>..\data\csvs\graph 3\nSybxTbphIR\N3\L8.csv</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>5402</v>
       </c>
       <c r="C72" t="n">
-        <v>49.3891151425398</v>
+        <v>60.57015920029619</v>
       </c>
       <c r="D72" t="n">
-        <v>0.2</v>
+        <v>109.0666666666667</v>
       </c>
       <c r="E72" t="n">
-        <v>922</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>37.79215705486608</v>
+        <v>73.03390746977914</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4148425582312413</v>
+        <v>1.029129743585427</v>
       </c>
       <c r="J72" t="n">
-        <v>0.218403296678375</v>
+        <v>0.8405355435672799</v>
       </c>
       <c r="K72" t="n">
-        <v>4.350413773424386</v>
+        <v>5.618896688852998</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>N1</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>nSybxw1118</t>
+          <t>nSybxTbphIR</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L8</t>
         </is>
       </c>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="n">
-        <v>0.0158955999999877</v>
+        <v>0.007447800000000282</v>
       </c>
       <c r="R72" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S72" t="b">
-        <v>1</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxw1118\N1\L3.csv</t>
+          <t>..\data\csvs\graph 3\nSybxTbphIR\N3\L9.csv</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>5402</v>
       </c>
       <c r="C73" t="n">
-        <v>0.1480932987782303</v>
+        <v>6.09033691225472</v>
       </c>
       <c r="D73" t="n">
-        <v>0.2666666666666667</v>
+        <v>10.96666666666667</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -5199,36 +5099,36 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>110.3868267280775</v>
+        <v>141.2541861429045</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6140561471986509</v>
+        <v>0.8354940032111854</v>
       </c>
       <c r="J73" t="n">
-        <v>0.4242640687118893</v>
+        <v>0.6184658438426192</v>
       </c>
       <c r="K73" t="n">
-        <v>5.345811444486316</v>
+        <v>5.807925619358433</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>N1</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>nSybxw1118</t>
+          <t>nSybxTbphIR</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L9</t>
         </is>
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="n">
-        <v>0.0126588258444367</v>
+        <v>0.009930399999994496</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
@@ -5241,38 +5141,38 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxw1118\N1\L4.csv</t>
+          <t>..\data\csvs\graph 3\nSybxw1118_29C\N1\L2.csv</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>5402</v>
+        <v>5401</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>29.03333333333333</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>2868</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>122.9457212147936</v>
+        <v>97.73228266839109</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6835381090518544</v>
+        <v>0.542957125935506</v>
       </c>
       <c r="J74" t="n">
-        <v>0.2107130530619556</v>
+        <v>0.4036087214121738</v>
       </c>
       <c r="K74" t="n">
-        <v>5.675077091987356</v>
+        <v>3.798170612281627</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -5281,21 +5181,21 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>nSybxw1118</t>
+          <t>nSybxw1118_29C</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="n">
-        <v>0.004965199999988428</v>
+        <v>0.01330677310220583</v>
       </c>
       <c r="R74" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="S74" t="b">
         <v>0</v>
@@ -5305,38 +5205,38 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxw1118\N1\L5.csv</t>
+          <t>..\data\csvs\graph 3\nSybxw1118_29C\N1\L3.csv</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>5402</v>
+        <v>5403</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>0.1</v>
+        <v>14.46666666666667</v>
       </c>
       <c r="E75" t="n">
-        <v>8</v>
+        <v>1210</v>
       </c>
       <c r="F75" t="n">
         <v>2</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H75" t="n">
-        <v>108.910923847972</v>
+        <v>80.88410096754518</v>
       </c>
       <c r="I75" t="n">
-        <v>0.6052848676248906</v>
+        <v>0.4494393459948797</v>
       </c>
       <c r="J75" t="n">
-        <v>0.4676527280687236</v>
+        <v>0.3059411708152721</v>
       </c>
       <c r="K75" t="n">
-        <v>6.189095248903584</v>
+        <v>4.986231041578455</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -5345,21 +5245,21 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>nSybxw1118</t>
+          <t>nSybxw1118_29C</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>L5</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="n">
-        <v>0.01710633027573655</v>
+        <v>0.009930399999976856</v>
       </c>
       <c r="R75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S75" t="b">
         <v>0</v>
@@ -5369,61 +5269,61 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxw1118\N2\L1.csv</t>
+          <t>..\data\csvs\graph 3\nSybxw1118_29C\N1\L4.csv</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>5403</v>
+        <v>5402</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>105.2191771478721</v>
+        <v>117.9929029055479</v>
       </c>
       <c r="I76" t="n">
-        <v>0.584334563945976</v>
+        <v>0.6553947578534413</v>
       </c>
       <c r="J76" t="n">
-        <v>0.426380112106463</v>
+        <v>0.5108815909776654</v>
       </c>
       <c r="K76" t="n">
-        <v>4.052221612893405</v>
+        <v>5.519304756941781</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>N1</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>nSybxw1118</t>
+          <t>nSybxw1118_29C</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="n">
-        <v>0.007447800000000282</v>
+        <v>0.01023602202616877</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S76" t="b">
         <v>0</v>
@@ -5433,88 +5333,84 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxw1118\N2\L2.csv</t>
+          <t>..\data\csvs\graph 3\nSybxw1118_29C\N1\L5.csv</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>5402</v>
+        <v>5403</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>62.56666666666667</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>1920</v>
+        <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>206.8881251522565</v>
+        <v>146.1539822006104</v>
       </c>
       <c r="I77" t="n">
-        <v>1.149591360357047</v>
+        <v>0.811665950762368</v>
       </c>
       <c r="J77" t="n">
-        <v>0.9823486154550725</v>
+        <v>0.6363961030679169</v>
       </c>
       <c r="K77" t="n">
-        <v>6.44190189307443</v>
+        <v>4.105618102064692</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>N1</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>nSybxw1118</t>
+          <t>nSybxw1118_29C</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="n">
-        <v>0.002482599999994214</v>
+        <v>0.004965199999988428</v>
       </c>
       <c r="R77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S77" t="b">
-        <v>1</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>unusually fast median speed</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxw1118\N2\L3.csv</t>
+          <t>..\data\csvs\graph 3\nSybxw1118_29C\N1\L6.csv</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>5402</v>
       </c>
       <c r="C78" t="n">
-        <v>24.21325435024065</v>
+        <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>48.03333333333333</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>1442</v>
+        <v>0</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -5523,66 +5419,62 @@
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>78.57035075670409</v>
+        <v>95.56009443115633</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5758882293430547</v>
+        <v>0.5307911188547842</v>
       </c>
       <c r="J78" t="n">
-        <v>0.2735867749724712</v>
+        <v>0.4080441152623504</v>
       </c>
       <c r="K78" t="n">
-        <v>4.268126052496738</v>
+        <v>3.483231258472553</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>N1</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>nSybxw1118</t>
+          <t>nSybxw1118_29C</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="n">
-        <v>0.007447800000000282</v>
+        <v>0.009930400000012135</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
       <c r="S78" t="b">
-        <v>1</v>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxw1118\N2\L4.csv</t>
+          <t>..\data\csvs\graph 3\nSybxw1118_29C\N2\L1.csv</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>5401</v>
+        <v>5403</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>15.84305015732001</v>
       </c>
       <c r="D79" t="n">
-        <v>8.9</v>
+        <v>28.53333333333333</v>
       </c>
       <c r="E79" t="n">
-        <v>276</v>
+        <v>73</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -5591,16 +5483,16 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>198.4299717536092</v>
+        <v>83.48278218070038</v>
       </c>
       <c r="I79" t="n">
-        <v>1.103410408268448</v>
+        <v>0.5509202519623871</v>
       </c>
       <c r="J79" t="n">
-        <v>0.8275868534479027</v>
+        <v>0.3900000000001569</v>
       </c>
       <c r="K79" t="n">
-        <v>5.726464878090107</v>
+        <v>3.445692963686597</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -5609,18 +5501,18 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>nSybxw1118</t>
+          <t>nSybxw1118_29C</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="n">
-        <v>0.002482599999976574</v>
+        <v>0.00555126236093593</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
@@ -5633,38 +5525,38 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxw1118\N2\L6.csv</t>
+          <t>..\data\csvs\graph 3\nSybxw1118_29C\N2\L2.csv</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>5401</v>
+        <v>5402</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>7.766666666666667</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>853</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>575</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>111.6697016144829</v>
+        <v>88.80946772157151</v>
       </c>
       <c r="I80" t="n">
-        <v>0.6203872311915716</v>
+        <v>0.4932945809381866</v>
       </c>
       <c r="J80" t="n">
-        <v>0.3899999999997962</v>
+        <v>0.3661966684716291</v>
       </c>
       <c r="K80" t="n">
-        <v>5.037142046835727</v>
+        <v>2.630779352207359</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -5673,21 +5565,21 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>nSybxw1118</t>
+          <t>nSybxw1118_29C</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>L6</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="n">
-        <v>0.007447799999995872</v>
+        <v>0.00555126236092804</v>
       </c>
       <c r="R80" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="S80" t="b">
         <v>0</v>
@@ -5697,17 +5589,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxw1118\N2\L7.csv</t>
+          <t>..\data\csvs\graph 3\nSybxw1118_29C\N2\L3.csv</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>5402</v>
       </c>
       <c r="C81" t="n">
-        <v>4.313217326915957</v>
+        <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>7.766666666666667</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
@@ -5719,16 +5611,16 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>108.461571829191</v>
+        <v>72.48578881669673</v>
       </c>
       <c r="I81" t="n">
-        <v>0.6296143875533532</v>
+        <v>0.4026242667100355</v>
       </c>
       <c r="J81" t="n">
-        <v>0.4657252408878</v>
+        <v>0.3000000000001535</v>
       </c>
       <c r="K81" t="n">
-        <v>3.394775397577987</v>
+        <v>2.99474539819327</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -5737,18 +5629,18 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>nSybxw1118</t>
+          <t>nSybxw1118_29C</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>L7</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="n">
-        <v>0.004965199999988428</v>
+        <v>0.009649076169509708</v>
       </c>
       <c r="R81" t="n">
         <v>0</v>
@@ -5761,20 +5653,20 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxw1118\N2\L8.csv</t>
+          <t>..\data\csvs\graph 3\nSybxw1118_29C\N2\L4.csv</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>5402</v>
       </c>
       <c r="C82" t="n">
-        <v>13.12476860422066</v>
+        <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>60.26666666666667</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>2492</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -5783,16 +5675,16 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>89.48670771772406</v>
+        <v>62.72413255803507</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5721656503690796</v>
+        <v>0.3484028840475933</v>
       </c>
       <c r="J82" t="n">
-        <v>0.3595623577524373</v>
+        <v>0.2846049894151649</v>
       </c>
       <c r="K82" t="n">
-        <v>5.249999999999957</v>
+        <v>3.180141506285579</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -5801,48 +5693,44 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>nSybxw1118</t>
+          <t>nSybxw1118_29C</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>L8</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>0.009050179769846192</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
       <c r="S82" t="b">
-        <v>1</v>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxw1118\N2\L9.csv</t>
+          <t>..\data\csvs\graph 3\nSybxw1118_29C\N2\L5.csv</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>5402</v>
+        <v>5403</v>
       </c>
       <c r="C83" t="n">
-        <v>0.1480932987782303</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -5851,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>74.68419659581954</v>
+        <v>66.68581729062142</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4154507505793782</v>
+        <v>0.3703395999108928</v>
       </c>
       <c r="J83" t="n">
-        <v>0.3088689042296562</v>
+        <v>0.2954657340538655</v>
       </c>
       <c r="K83" t="n">
-        <v>3.403645104883809</v>
+        <v>2.441823089414985</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -5869,18 +5757,18 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>nSybxw1118</t>
+          <t>nSybxw1118_29C</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>L9</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="n">
-        <v>0.007850670519138035</v>
+        <v>0.008951141596460717</v>
       </c>
       <c r="R83" t="n">
         <v>0</v>
@@ -5893,88 +5781,84 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxw1118\N3\L1.csv</t>
+          <t>..\data\csvs\graph 3\nSybxw1118_29C\N2\L6.csv</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>5402</v>
       </c>
       <c r="C84" t="n">
-        <v>34.89448352462051</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>62.83333333333334</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>80.52028163573186</v>
+        <v>73.39095548047123</v>
       </c>
       <c r="I84" t="n">
-        <v>0.6870331197588044</v>
+        <v>0.4076520393286682</v>
       </c>
       <c r="J84" t="n">
-        <v>0.4719579621500334</v>
+        <v>0.3059411708157319</v>
       </c>
       <c r="K84" t="n">
-        <v>5.272921391411036</v>
+        <v>3.231098884280669</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>nSybxw1118</t>
+          <t>nSybxw1118_29C</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="n">
-        <v>0.009930399999994496</v>
+        <v>0.007850670519138035</v>
       </c>
       <c r="R84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S84" t="b">
-        <v>1</v>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxw1118\N3\L2.csv</t>
+          <t>..\data\csvs\graph 3\nSybxw1118_29C\N2\L7.csv</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>5402</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>18.04887078859682</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>32.5</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>453</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -5983,36 +5867,36 @@
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>162.850693501779</v>
+        <v>81.99505856353613</v>
       </c>
       <c r="I85" t="n">
-        <v>0.9045585641646677</v>
+        <v>0.5557731036841581</v>
       </c>
       <c r="J85" t="n">
-        <v>0.7003570517955996</v>
+        <v>0.3649657518179187</v>
       </c>
       <c r="K85" t="n">
-        <v>6.024699162613728</v>
+        <v>4.041546733615662</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>nSybxw1118</t>
+          <t>nSybxw1118_29C</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L7</t>
         </is>
       </c>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="n">
-        <v>0.004965199999988428</v>
+        <v>0.004965199999997248</v>
       </c>
       <c r="R85" t="n">
         <v>0</v>
@@ -6025,20 +5909,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxw1118\N3\L3.csv</t>
+          <t>..\data\csvs\graph 3\nSybxw1118_29C\N2\L8.csv</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>5402</v>
+        <v>5403</v>
       </c>
       <c r="C86" t="n">
-        <v>6.460570159200296</v>
+        <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>11.63333333333333</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>1292</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -6047,66 +5931,62 @@
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>79.71017195643083</v>
+        <v>92.30658204978977</v>
       </c>
       <c r="I86" t="n">
-        <v>0.4733383132804682</v>
+        <v>0.512624483801128</v>
       </c>
       <c r="J86" t="n">
-        <v>0.3088689042295527</v>
+        <v>0.394588393138722</v>
       </c>
       <c r="K86" t="n">
-        <v>4.697371605483276</v>
+        <v>3.147713455828005</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>nSybxw1118</t>
+          <t>nSybxw1118_29C</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L8</t>
         </is>
       </c>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="n">
-        <v>0.004965199999988428</v>
+        <v>0.007447800000000282</v>
       </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
       <c r="S86" t="b">
-        <v>1</v>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxw1118\N3\L4.csv</t>
+          <t>..\data\csvs\graph 3\nSybxw1118_29C\N2\L9.csv</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>5403</v>
+        <v>5402</v>
       </c>
       <c r="C87" t="n">
-        <v>24.04219877845641</v>
+        <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>43.3</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -6115,30 +5995,30 @@
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>108.2655374238604</v>
+        <v>104.7288912028017</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7916076341008558</v>
+        <v>0.5817194475252827</v>
       </c>
       <c r="J87" t="n">
-        <v>0.5770615218503026</v>
+        <v>0.4500000000000171</v>
       </c>
       <c r="K87" t="n">
-        <v>4.867864007960829</v>
+        <v>3.274263275914213</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>nSybxw1118</t>
+          <t>nSybxw1118_29C</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>L9</t>
         </is>
       </c>
       <c r="O87" t="inlineStr"/>
@@ -6150,18 +6030,14 @@
         <v>0</v>
       </c>
       <c r="S87" t="b">
-        <v>1</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxw1118\N3\L5.csv</t>
+          <t>..\data\csvs\graph 3\nSybxw1118_29C\N3\L1.csv</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -6171,10 +6047,10 @@
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>70.03333333333333</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>2549</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -6183,16 +6059,16 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>76.98182978812399</v>
+        <v>81.35244391115279</v>
       </c>
       <c r="I88" t="n">
-        <v>0.4275976474067247</v>
+        <v>0.4518743412950535</v>
       </c>
       <c r="J88" t="n">
-        <v>0.1637508927598055</v>
+        <v>0.3354101966248541</v>
       </c>
       <c r="K88" t="n">
-        <v>3.195387300469311</v>
+        <v>2.984359227707146</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -6201,18 +6077,18 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>nSybxw1118</t>
+          <t>nSybxw1118_29C</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>L5</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>0.008951141596460717</v>
       </c>
       <c r="R88" t="n">
         <v>0</v>
@@ -6225,7 +6101,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxw1118\N3\L6.csv</t>
+          <t>..\data\csvs\graph 3\nSybxw1118_29C\N3\L2.csv</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -6247,16 +6123,16 @@
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>71.26991664115283</v>
+        <v>92.78013575476538</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3958706719560423</v>
+        <v>0.5153497634961972</v>
       </c>
       <c r="J89" t="n">
-        <v>0.3059411708154812</v>
+        <v>0.3758989225843267</v>
       </c>
       <c r="K89" t="n">
-        <v>3.501785258978633</v>
+        <v>3.902883549377256</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -6265,18 +6141,18 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>nSybxw1118</t>
+          <t>nSybxw1118_29C</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>L6</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="n">
-        <v>0.01117622584444016</v>
+        <v>0.007447800000000282</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
@@ -6289,38 +6165,38 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxw1118\N3\L7.csv</t>
+          <t>..\data\csvs\graph 3\nSybxw1118_29C\N3\L3.csv</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>5403</v>
+        <v>5402</v>
       </c>
       <c r="C90" t="n">
-        <v>33.48139922265408</v>
+        <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>2339</v>
+        <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>1817</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>29.80484699893915</v>
+        <v>60.08215823695775</v>
       </c>
       <c r="I90" t="n">
-        <v>0.2489268958708727</v>
+        <v>0.3337279665078194</v>
       </c>
       <c r="J90" t="n">
-        <v>0.07269073201435233</v>
+        <v>0.2473863375371552</v>
       </c>
       <c r="K90" t="n">
-        <v>3.180438296069147</v>
+        <v>2.923576576729408</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -6329,66 +6205,62 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>nSybxw1118</t>
+          <t>nSybxw1118_29C</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>L7</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>0.008743526092330046</v>
       </c>
       <c r="R90" t="n">
-        <v>283</v>
+        <v>0</v>
       </c>
       <c r="S90" t="b">
-        <v>1</v>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxw1118\N3\L8.csv</t>
+          <t>..\data\csvs\graph 3\nSybxw1118_29C\N3\L4.csv</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>5402</v>
       </c>
       <c r="C91" t="n">
-        <v>48.00074046649389</v>
+        <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>86.43333333333334</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>94.41699785323205</v>
+        <v>68.6454763528275</v>
       </c>
       <c r="I91" t="n">
-        <v>1.008728609543077</v>
+        <v>0.3812931476735465</v>
       </c>
       <c r="J91" t="n">
-        <v>0.75538069872102</v>
+        <v>0.2954657340538655</v>
       </c>
       <c r="K91" t="n">
-        <v>6.484933612878095</v>
+        <v>2.79451247984338</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -6397,48 +6269,44 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>nSybxw1118</t>
+          <t>nSybxw1118_29C</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>L8</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
       <c r="Q91" t="n">
-        <v>0.004965199999988428</v>
+        <v>0.007447800000000282</v>
       </c>
       <c r="R91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S91" t="b">
-        <v>1</v>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>high untracked %</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>..\data\csvs\graph 2\nSybxw1118\N3\L9.csv</t>
+          <t>..\data\csvs\graph 3\nSybxw1118_29C\N3\L5.csv</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>5401</v>
+        <v>5403</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>75.53333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E92" t="n">
-        <v>2569</v>
+        <v>1</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -6447,16 +6315,16 @@
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>80.25007699704958</v>
+        <v>75.46117343867581</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4458337610947199</v>
+        <v>0.4191511207480604</v>
       </c>
       <c r="J92" t="n">
-        <v>0.1533876182349029</v>
+        <v>0.3088689042296562</v>
       </c>
       <c r="K92" t="n">
-        <v>3.396763165132372</v>
+        <v>4.428329256051315</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -6465,18 +6333,18 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>nSybxw1118</t>
+          <t>nSybxw1118_29C</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>L9</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="n">
-        <v>0.004965199999988428</v>
+        <v>0.009930400000012135</v>
       </c>
       <c r="R92" t="n">
         <v>0</v>
@@ -6485,6 +6353,198 @@
         <v>0</v>
       </c>
       <c r="T92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 3\nSybxw1118_29C\N3\L6.csv</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>5403</v>
+      </c>
+      <c r="C93" t="n">
+        <v>14.91763834906533</v>
+      </c>
+      <c r="D93" t="n">
+        <v>26.86666666666667</v>
+      </c>
+      <c r="E93" t="n">
+        <v>15</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>82.76319346435579</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.5402297223521919</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0.3841874542460576</v>
+      </c>
+      <c r="K93" t="n">
+        <v>3.679252641502019</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>nSybxw1118_29C</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="n">
+        <v>0.00555126236092804</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="b">
+        <v>0</v>
+      </c>
+      <c r="T93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 3\nSybxw1118_29C\N3\L7.csv</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>104.0968382558564</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.5782086924043127</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0.4743416490252165</v>
+      </c>
+      <c r="K94" t="n">
+        <v>3.918992217394582</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>nSybxw1118_29C</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="n">
+        <v>0.005551262360951707</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="b">
+        <v>0</v>
+      </c>
+      <c r="T94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>..\data\csvs\graph 3\nSybxw1118_29C\N3\L9.csv</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>5402</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>106.5093710889058</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.5916091710178065</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0.4326661530556163</v>
+      </c>
+      <c r="K95" t="n">
+        <v>3.781071276768013</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>nSybxw1118_29C</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="n">
+        <v>0.007447800000000282</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="b">
+        <v>0</v>
+      </c>
+      <c r="T95" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
